--- a/Snobol Functions.xlsx
+++ b/Snobol Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcooper\source\repos\Spitbol4Win\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73041B5D-AE42-4120-B992-9B1600DB29AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9999EBB-0BFF-46B9-9F9A-5957E27CCFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13956" yWindow="2880" windowWidth="19836" windowHeight="18816" activeTab="2" xr2:uid="{14808CA3-9D70-46D1-8654-4F03110B5BF1}"/>
+    <workbookView xWindow="29604" yWindow="5004" windowWidth="19860" windowHeight="18816" activeTab="2" xr2:uid="{14808CA3-9D70-46D1-8654-4F03110B5BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Keywords" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Errors" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Errors!$A$1:$C$331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Errors!$A$1:$C$334</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Keywords!$A$1:$D$16631</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Testing!$A$1:$C$135</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="611">
   <si>
     <t>any</t>
   </si>
@@ -870,306 +870,6 @@
     <t>Reserved</t>
   </si>
   <si>
-    <t>0       (no err 0 in build; 'No error' is a reporting convention)</t>
-  </si>
-  <si>
-    <t>1       addition left operand is not numeric</t>
-  </si>
-  <si>
-    <t>2       addition right operand is not numeric</t>
-  </si>
-  <si>
-    <t>3       addition caused integer overflow</t>
-  </si>
-  <si>
-    <t>4       affirmation operand is not numeric</t>
-  </si>
-  <si>
-    <t>5       alternation right operand is not pattern</t>
-  </si>
-  <si>
-    <t>6       alternation left operand is not pattern</t>
-  </si>
-  <si>
-    <t>7       compilation error encountered during execution</t>
-  </si>
-  <si>
-    <t>8       concatenation left operand is not a string or pattern</t>
-  </si>
-  <si>
-    <t>9       concatenation right operand is not a string or pattern</t>
-  </si>
-  <si>
-    <t>10      negation operand is not numeric</t>
-  </si>
-  <si>
-    <t>11      negation caused integer overflow</t>
-  </si>
-  <si>
-    <t>12      division left operand is not numeric</t>
-  </si>
-  <si>
-    <t>13      division right operand is not numeric</t>
-  </si>
-  <si>
-    <t>14      division caused integer overflow</t>
-  </si>
-  <si>
-    <t>15      exponentiation right operand is not numeric</t>
-  </si>
-  <si>
-    <t>16      exponentiation left operand is not numeric</t>
-  </si>
-  <si>
-    <t>17      exponentiation caused integer overflow</t>
-  </si>
-  <si>
-    <t>18      exponentiation result is undefined</t>
-  </si>
-  <si>
-    <t>19      exponentiation right operand is negative</t>
-  </si>
-  <si>
-    <t>20      goto evaluation failure</t>
-  </si>
-  <si>
-    <t>21      function called by name returned a value</t>
-  </si>
-  <si>
-    <t>22      undefined function called</t>
-  </si>
-  <si>
-    <t>23      goto operand is not a natural variable</t>
-  </si>
-  <si>
-    <t>24      goto operand in direct goto is not code</t>
-  </si>
-  <si>
-    <t>25      immediate assignment left operand is not pattern</t>
-  </si>
-  <si>
-    <t>26      multiplication left operand is not numeric</t>
-  </si>
-  <si>
-    <t>27      multiplication right operand is not numeric</t>
-  </si>
-  <si>
-    <t>28      multiplication caused integer overflow</t>
-  </si>
-  <si>
-    <t>29      undefined operator referenced</t>
-  </si>
-  <si>
-    <t>30      pattern assignment left operand is not pattern</t>
-  </si>
-  <si>
-    <t>31      pattern replacement right operand is not a string</t>
-  </si>
-  <si>
-    <t>32      subtraction left operand is not numeric</t>
-  </si>
-  <si>
-    <t>33      subtraction right operand is not numeric</t>
-  </si>
-  <si>
-    <t>34      subtraction caused integer overflow</t>
-  </si>
-  <si>
-    <t>35      unexpected failure in -nofail mode</t>
-  </si>
-  <si>
-    <t>36      goto abort with no preceding error</t>
-  </si>
-  <si>
-    <t>37      goto continue with no preceding error</t>
-  </si>
-  <si>
-    <t>38      goto undefined label</t>
-  </si>
-  <si>
-    <t>39      external function argument is not a string</t>
-  </si>
-  <si>
-    <t>40      external function argument is not integer</t>
-  </si>
-  <si>
-    <t>41      field function argument is wrong datatype</t>
-  </si>
-  <si>
-    <t>42      attempt to change value of protected variable</t>
-  </si>
-  <si>
-    <t>43      any evaluated argument is not a string</t>
-  </si>
-  <si>
-    <t>44      break evaluated argument is not a string</t>
-  </si>
-  <si>
-    <t>45      breakx evaluated argument is not a string</t>
-  </si>
-  <si>
-    <t>46      expression does not evaluate to pattern</t>
-  </si>
-  <si>
-    <t>47      len evaluated argument is not integer</t>
-  </si>
-  <si>
-    <t>48      len evaluated argument is negative or too large</t>
-  </si>
-  <si>
-    <t>49      notany evaluated argument is not a string</t>
-  </si>
-  <si>
-    <t>50      pos evaluated argument is not integer</t>
-  </si>
-  <si>
-    <t>51      pos evaluated argument is negative or too large</t>
-  </si>
-  <si>
-    <t>52      rpos evaluated argument is not integer</t>
-  </si>
-  <si>
-    <t>53      rpos evaluated argument is negative or too large</t>
-  </si>
-  <si>
-    <t>54      rtab evaluated argument is not integer</t>
-  </si>
-  <si>
-    <t>55      rtab evaluated argument is negative or too large</t>
-  </si>
-  <si>
-    <t>56      span evaluated argument is not a string</t>
-  </si>
-  <si>
-    <t>57      tab evaluated argument is not integer</t>
-  </si>
-  <si>
-    <t>58      tab evaluated argument is negative or too large</t>
-  </si>
-  <si>
-    <t>59      any argument is not a string or expression</t>
-  </si>
-  <si>
-    <t>60      apply first arg is not natural variable name</t>
-  </si>
-  <si>
-    <t>61      arbno argument is not pattern</t>
-  </si>
-  <si>
-    <t>62      arg second argument is not integer</t>
-  </si>
-  <si>
-    <t>63      arg first argument is not program function name</t>
-  </si>
-  <si>
-    <t>64      array first argument is not integer or string</t>
-  </si>
-  <si>
-    <t>65      array first argument lower bound is not integer</t>
-  </si>
-  <si>
-    <t>66      array first argument upper bound is not integer</t>
-  </si>
-  <si>
-    <t>67      array dimension is zero, negative or out of range</t>
-  </si>
-  <si>
-    <t>68      array size exceeds maximum permitted</t>
-  </si>
-  <si>
-    <t>69      break argument is not a string or expression</t>
-  </si>
-  <si>
-    <t>70      breakx argument is not a string or expression</t>
-  </si>
-  <si>
-    <t>71      clear argument is not a string</t>
-  </si>
-  <si>
-    <t>72      clear argument has null variable name</t>
-  </si>
-  <si>
-    <t>73      collect argument is not integer</t>
-  </si>
-  <si>
-    <t>74      convert second argument is not a string</t>
-  </si>
-  <si>
-    <t>75      data argument is not a string</t>
-  </si>
-  <si>
-    <t>76      data argument is null</t>
-  </si>
-  <si>
-    <t>77      data argument is missing a left paren</t>
-  </si>
-  <si>
-    <t>78      data argument has null datatype name</t>
-  </si>
-  <si>
-    <t>79      data argument is missing a right paren</t>
-  </si>
-  <si>
-    <t>80      data argument has null field name</t>
-  </si>
-  <si>
-    <t>81      define first argument is not a string</t>
-  </si>
-  <si>
-    <t>82      define first argument is null</t>
-  </si>
-  <si>
-    <t>83      define first argument is missing a left paren</t>
-  </si>
-  <si>
-    <t>84      define first argument has null function name</t>
-  </si>
-  <si>
-    <t>85      null arg name or missing ) in define first arg.</t>
-  </si>
-  <si>
-    <t>86      define function entry point is not defined label</t>
-  </si>
-  <si>
-    <t>87      detach argument is not appropriate name</t>
-  </si>
-  <si>
-    <t>88      dump argument is not integer</t>
-  </si>
-  <si>
-    <t>89      dump argument is negative or too large</t>
-  </si>
-  <si>
-    <t>90      dupl second argument is not integer</t>
-  </si>
-  <si>
-    <t>91      dupl first argument is not a string or pattern</t>
-  </si>
-  <si>
-    <t>92      eject argument is not a suitable name</t>
-  </si>
-  <si>
-    <t>93      eject file does not exist</t>
-  </si>
-  <si>
-    <t>94      eject file does not permit page eject</t>
-  </si>
-  <si>
-    <t>95      eject caused non-recoverable output error</t>
-  </si>
-  <si>
-    <t>96      endfile argument is not a suitable name</t>
-  </si>
-  <si>
-    <t>97      endfile argument is null</t>
-  </si>
-  <si>
-    <t>98      endfile file does not exist</t>
-  </si>
-  <si>
-    <t>99      endfile file does not permit endfile</t>
-  </si>
-  <si>
     <t>100     endfile caused non-recoverable output error</t>
   </si>
   <si>
@@ -1842,9 +1542,6 @@
     <t>323     sin argument is out of range</t>
   </si>
   <si>
-    <t>324     set second argument not numeric</t>
-  </si>
-  <si>
     <t>325     RESERVED (undefined in build)</t>
   </si>
   <si>
@@ -1867,6 +1564,318 @@
   </si>
   <si>
     <t>332     goto continue with error in failure goto</t>
+  </si>
+  <si>
+    <t>Unreachable</t>
+  </si>
+  <si>
+    <t>UNUSED</t>
+  </si>
+  <si>
+    <t>000       (no err 0 in build; 'No error' is a reporting convention)</t>
+  </si>
+  <si>
+    <t>001       addition left operand is not numeric</t>
+  </si>
+  <si>
+    <t>002       addition right operand is not numeric</t>
+  </si>
+  <si>
+    <t>003       addition caused integer overflow</t>
+  </si>
+  <si>
+    <t>004       affirmation operand is not numeric</t>
+  </si>
+  <si>
+    <t>005       alternation right operand is not pattern</t>
+  </si>
+  <si>
+    <t>006       alternation left operand is not pattern</t>
+  </si>
+  <si>
+    <t>007       compilation error encountered during execution</t>
+  </si>
+  <si>
+    <t>008       concatenation left operand is not a string or pattern</t>
+  </si>
+  <si>
+    <t>009       concatenation right operand is not a string or pattern</t>
+  </si>
+  <si>
+    <t>010      negation operand is not numeric</t>
+  </si>
+  <si>
+    <t>011      negation caused integer overflow</t>
+  </si>
+  <si>
+    <t>012      division left operand is not numeric</t>
+  </si>
+  <si>
+    <t>013      division right operand is not numeric</t>
+  </si>
+  <si>
+    <t>014      division caused integer overflow</t>
+  </si>
+  <si>
+    <t>015      exponentiation right operand is not numeric</t>
+  </si>
+  <si>
+    <t>016      exponentiation left operand is not numeric</t>
+  </si>
+  <si>
+    <t>017      exponentiation caused integer overflow</t>
+  </si>
+  <si>
+    <t>018      exponentiation result is undefined</t>
+  </si>
+  <si>
+    <t>019      exponentiation right operand is negative</t>
+  </si>
+  <si>
+    <t>020      goto evaluation failure</t>
+  </si>
+  <si>
+    <t>021      function called by name returned a value</t>
+  </si>
+  <si>
+    <t>022      undefined function called</t>
+  </si>
+  <si>
+    <t>023      goto operand is not a natural variable</t>
+  </si>
+  <si>
+    <t>024      goto operand in direct goto is not code</t>
+  </si>
+  <si>
+    <t>025      immediate assignment left operand is not pattern</t>
+  </si>
+  <si>
+    <t>026      multiplication left operand is not numeric</t>
+  </si>
+  <si>
+    <t>027      multiplication right operand is not numeric</t>
+  </si>
+  <si>
+    <t>028      multiplication caused integer overflow</t>
+  </si>
+  <si>
+    <t>029      undefined operator referenced</t>
+  </si>
+  <si>
+    <t>030      pattern assignment left operand is not pattern</t>
+  </si>
+  <si>
+    <t>031      pattern replacement right operand is not a string</t>
+  </si>
+  <si>
+    <t>032      subtraction left operand is not numeric</t>
+  </si>
+  <si>
+    <t>033      subtraction right operand is not numeric</t>
+  </si>
+  <si>
+    <t>034      subtraction caused integer overflow</t>
+  </si>
+  <si>
+    <t>035      unexpected failure in -nofail mode</t>
+  </si>
+  <si>
+    <t>036      goto abort with no preceding error</t>
+  </si>
+  <si>
+    <t>037      goto continue with no preceding error</t>
+  </si>
+  <si>
+    <t>038      goto undefined label</t>
+  </si>
+  <si>
+    <t>039      external function argument is not a string</t>
+  </si>
+  <si>
+    <t>040      external function argument is not integer</t>
+  </si>
+  <si>
+    <t>041      field function argument is wrong datatype</t>
+  </si>
+  <si>
+    <t>042      attempt to change value of protected variable</t>
+  </si>
+  <si>
+    <t>043      any evaluated argument is not a string</t>
+  </si>
+  <si>
+    <t>044      break evaluated argument is not a string</t>
+  </si>
+  <si>
+    <t>045      breakx evaluated argument is not a string</t>
+  </si>
+  <si>
+    <t>046      expression does not evaluate to pattern</t>
+  </si>
+  <si>
+    <t>047      len evaluated argument is not integer</t>
+  </si>
+  <si>
+    <t>048      len evaluated argument is negative or too large</t>
+  </si>
+  <si>
+    <t>049      notany evaluated argument is not a string</t>
+  </si>
+  <si>
+    <t>050      pos evaluated argument is not integer</t>
+  </si>
+  <si>
+    <t>051      pos evaluated argument is negative or too large</t>
+  </si>
+  <si>
+    <t>052      rpos evaluated argument is not integer</t>
+  </si>
+  <si>
+    <t>053      rpos evaluated argument is negative or too large</t>
+  </si>
+  <si>
+    <t>054      rtab evaluated argument is not integer</t>
+  </si>
+  <si>
+    <t>055      rtab evaluated argument is negative or too large</t>
+  </si>
+  <si>
+    <t>056      span evaluated argument is not a string</t>
+  </si>
+  <si>
+    <t>057      tab evaluated argument is not integer</t>
+  </si>
+  <si>
+    <t>058      tab evaluated argument is negative or too large</t>
+  </si>
+  <si>
+    <t>059      any argument is not a string or expression</t>
+  </si>
+  <si>
+    <t>060      apply first arg is not natural variable name</t>
+  </si>
+  <si>
+    <t>061      arbno argument is not pattern</t>
+  </si>
+  <si>
+    <t>062      arg second argument is not integer</t>
+  </si>
+  <si>
+    <t>063      arg first argument is not program function name</t>
+  </si>
+  <si>
+    <t>064      array first argument is not integer or string</t>
+  </si>
+  <si>
+    <t>065      array first argument lower bound is not integer</t>
+  </si>
+  <si>
+    <t>066      array first argument upper bound is not integer</t>
+  </si>
+  <si>
+    <t>067      array dimension is zero, negative or out of range</t>
+  </si>
+  <si>
+    <t>068      array size exceeds maximum permitted</t>
+  </si>
+  <si>
+    <t>069      break argument is not a string or expression</t>
+  </si>
+  <si>
+    <t>070      breakx argument is not a string or expression</t>
+  </si>
+  <si>
+    <t>071      clear argument is not a string</t>
+  </si>
+  <si>
+    <t>072      clear argument has null variable name</t>
+  </si>
+  <si>
+    <t>073      collect argument is not integer</t>
+  </si>
+  <si>
+    <t>074      convert second argument is not a string</t>
+  </si>
+  <si>
+    <t>075      data argument is not a string</t>
+  </si>
+  <si>
+    <t>076      data argument is null</t>
+  </si>
+  <si>
+    <t>077      data argument is missing a left paren</t>
+  </si>
+  <si>
+    <t>078      data argument has null datatype name</t>
+  </si>
+  <si>
+    <t>079      data argument is missing a right paren</t>
+  </si>
+  <si>
+    <t>080      data argument has null field name</t>
+  </si>
+  <si>
+    <t>081      define first argument is not a string</t>
+  </si>
+  <si>
+    <t>082      define first argument is null</t>
+  </si>
+  <si>
+    <t>083      define first argument is missing a left paren</t>
+  </si>
+  <si>
+    <t>084      define first argument has null function name</t>
+  </si>
+  <si>
+    <t>085      null arg name or missing ) in define first arg.</t>
+  </si>
+  <si>
+    <t>086      define function entry point is not defined label</t>
+  </si>
+  <si>
+    <t>087      detach argument is not appropriate name</t>
+  </si>
+  <si>
+    <t>088      dump argument is not integer</t>
+  </si>
+  <si>
+    <t>089      dump argument is negative or too large</t>
+  </si>
+  <si>
+    <t>090      dupl second argument is not integer</t>
+  </si>
+  <si>
+    <t>091      dupl first argument is not a string or pattern</t>
+  </si>
+  <si>
+    <t>092      eject argument is not a suitable name</t>
+  </si>
+  <si>
+    <t>093      eject file does not exist</t>
+  </si>
+  <si>
+    <t>094      eject file does not permit page eject</t>
+  </si>
+  <si>
+    <t>095      eject caused non-recoverable output error</t>
+  </si>
+  <si>
+    <t>096      endfile argument is not a suitable name</t>
+  </si>
+  <si>
+    <t>097      endfile argument is null</t>
+  </si>
+  <si>
+    <t>098      endfile file does not exist</t>
+  </si>
+  <si>
+    <t>099      endfile file does not permit endfile</t>
+  </si>
+  <si>
+    <t>324     set second argument not numeric (NOT FIRED)</t>
+  </si>
+  <si>
+    <t>testing</t>
   </si>
 </sst>
 </file>
@@ -54653,7 +54662,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
-  <dimension ref="A1:C334"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -54674,7 +54684,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>509</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -54685,7 +54695,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>276</v>
+        <v>510</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -54696,7 +54706,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>511</v>
       </c>
       <c r="B4" s="5">
         <v>2</v>
@@ -54707,7 +54717,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>278</v>
+        <v>512</v>
       </c>
       <c r="B5" s="5">
         <v>3</v>
@@ -54718,7 +54728,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>513</v>
       </c>
       <c r="B6" s="5">
         <v>4</v>
@@ -54729,7 +54739,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>514</v>
       </c>
       <c r="B7" s="5">
         <v>5</v>
@@ -54740,7 +54750,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>515</v>
       </c>
       <c r="B8" s="5">
         <v>6</v>
@@ -54751,18 +54761,18 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>516</v>
       </c>
       <c r="B9" s="5">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>283</v>
+        <v>517</v>
       </c>
       <c r="B10" s="5">
         <v>8</v>
@@ -54773,7 +54783,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>518</v>
       </c>
       <c r="B11" s="5">
         <v>9</v>
@@ -54784,7 +54794,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>285</v>
+        <v>519</v>
       </c>
       <c r="B12" s="5">
         <v>10</v>
@@ -54795,7 +54805,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>520</v>
       </c>
       <c r="B13" s="5">
         <v>11</v>
@@ -54806,7 +54816,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>521</v>
       </c>
       <c r="B14" s="5">
         <v>12</v>
@@ -54817,7 +54827,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>288</v>
+        <v>522</v>
       </c>
       <c r="B15" s="5">
         <v>13</v>
@@ -54828,7 +54838,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>523</v>
       </c>
       <c r="B16" s="5">
         <v>14</v>
@@ -54839,7 +54849,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>290</v>
+        <v>524</v>
       </c>
       <c r="B17" s="5">
         <v>15</v>
@@ -54850,7 +54860,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>291</v>
+        <v>525</v>
       </c>
       <c r="B18" s="5">
         <v>16</v>
@@ -54861,7 +54871,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>292</v>
+        <v>526</v>
       </c>
       <c r="B19" s="5">
         <v>17</v>
@@ -54872,7 +54882,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>527</v>
       </c>
       <c r="B20" s="5">
         <v>18</v>
@@ -54881,20 +54891,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>528</v>
       </c>
       <c r="B21" s="5">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="b">
-        <v>0</v>
+      <c r="C21" s="6" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>529</v>
       </c>
       <c r="B22" s="5">
         <v>20</v>
@@ -54905,7 +54915,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>530</v>
       </c>
       <c r="B23" s="5">
         <v>21</v>
@@ -54916,7 +54926,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>531</v>
       </c>
       <c r="B24" s="5">
         <v>22</v>
@@ -54927,7 +54937,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>298</v>
+        <v>532</v>
       </c>
       <c r="B25" s="5">
         <v>23</v>
@@ -54938,7 +54948,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>299</v>
+        <v>533</v>
       </c>
       <c r="B26" s="5">
         <v>24</v>
@@ -54949,7 +54959,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>300</v>
+        <v>534</v>
       </c>
       <c r="B27" s="5">
         <v>25</v>
@@ -54960,7 +54970,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>301</v>
+        <v>535</v>
       </c>
       <c r="B28" s="5">
         <v>26</v>
@@ -54971,7 +54981,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>302</v>
+        <v>536</v>
       </c>
       <c r="B29" s="5">
         <v>27</v>
@@ -54982,7 +54992,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>303</v>
+        <v>537</v>
       </c>
       <c r="B30" s="5">
         <v>28</v>
@@ -54993,7 +55003,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>304</v>
+        <v>538</v>
       </c>
       <c r="B31" s="5">
         <v>29</v>
@@ -55004,7 +55014,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>305</v>
+        <v>539</v>
       </c>
       <c r="B32" s="5">
         <v>30</v>
@@ -55015,7 +55025,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>306</v>
+        <v>540</v>
       </c>
       <c r="B33" s="5">
         <v>31</v>
@@ -55026,7 +55036,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>307</v>
+        <v>541</v>
       </c>
       <c r="B34" s="5">
         <v>32</v>
@@ -55037,7 +55047,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>308</v>
+        <v>542</v>
       </c>
       <c r="B35" s="5">
         <v>33</v>
@@ -55048,7 +55058,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>309</v>
+        <v>543</v>
       </c>
       <c r="B36" s="5">
         <v>34</v>
@@ -55059,7 +55069,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>310</v>
+        <v>544</v>
       </c>
       <c r="B37" s="5">
         <v>35</v>
@@ -55070,7 +55080,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>311</v>
+        <v>545</v>
       </c>
       <c r="B38" s="5">
         <v>36</v>
@@ -55081,7 +55091,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>312</v>
+        <v>546</v>
       </c>
       <c r="B39" s="5">
         <v>37</v>
@@ -55092,7 +55102,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>313</v>
+        <v>547</v>
       </c>
       <c r="B40" s="5">
         <v>38</v>
@@ -55103,7 +55113,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>314</v>
+        <v>548</v>
       </c>
       <c r="B41" s="5">
         <v>39</v>
@@ -55114,7 +55124,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>315</v>
+        <v>549</v>
       </c>
       <c r="B42" s="5">
         <v>40</v>
@@ -55125,7 +55135,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>316</v>
+        <v>550</v>
       </c>
       <c r="B43" s="5">
         <v>41</v>
@@ -55136,7 +55146,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>317</v>
+        <v>551</v>
       </c>
       <c r="B44" s="5">
         <v>42</v>
@@ -55147,7 +55157,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>318</v>
+        <v>552</v>
       </c>
       <c r="B45" s="5">
         <v>43</v>
@@ -55158,7 +55168,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>319</v>
+        <v>553</v>
       </c>
       <c r="B46" s="5">
         <v>44</v>
@@ -55169,7 +55179,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>320</v>
+        <v>554</v>
       </c>
       <c r="B47" s="5">
         <v>45</v>
@@ -55180,7 +55190,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>321</v>
+        <v>555</v>
       </c>
       <c r="B48" s="5">
         <v>46</v>
@@ -55191,7 +55201,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>322</v>
+        <v>556</v>
       </c>
       <c r="B49" s="5">
         <v>47</v>
@@ -55202,7 +55212,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>323</v>
+        <v>557</v>
       </c>
       <c r="B50" s="5">
         <v>48</v>
@@ -55213,7 +55223,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>324</v>
+        <v>558</v>
       </c>
       <c r="B51" s="5">
         <v>49</v>
@@ -55224,7 +55234,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>325</v>
+        <v>559</v>
       </c>
       <c r="B52" s="5">
         <v>50</v>
@@ -55235,7 +55245,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>326</v>
+        <v>560</v>
       </c>
       <c r="B53" s="5">
         <v>51</v>
@@ -55246,7 +55256,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>327</v>
+        <v>561</v>
       </c>
       <c r="B54" s="5">
         <v>52</v>
@@ -55257,7 +55267,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>328</v>
+        <v>562</v>
       </c>
       <c r="B55" s="5">
         <v>53</v>
@@ -55268,7 +55278,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>329</v>
+        <v>563</v>
       </c>
       <c r="B56" s="5">
         <v>54</v>
@@ -55279,7 +55289,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>330</v>
+        <v>564</v>
       </c>
       <c r="B57" s="5">
         <v>55</v>
@@ -55290,7 +55300,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>331</v>
+        <v>565</v>
       </c>
       <c r="B58" s="5">
         <v>56</v>
@@ -55301,7 +55311,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>332</v>
+        <v>566</v>
       </c>
       <c r="B59" s="5">
         <v>57</v>
@@ -55312,7 +55322,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>333</v>
+        <v>567</v>
       </c>
       <c r="B60" s="5">
         <v>58</v>
@@ -55323,7 +55333,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>334</v>
+        <v>568</v>
       </c>
       <c r="B61" s="5">
         <v>59</v>
@@ -55334,7 +55344,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>335</v>
+        <v>569</v>
       </c>
       <c r="B62" s="5">
         <v>60</v>
@@ -55345,7 +55355,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>336</v>
+        <v>570</v>
       </c>
       <c r="B63" s="5">
         <v>61</v>
@@ -55356,7 +55366,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>337</v>
+        <v>571</v>
       </c>
       <c r="B64" s="5">
         <v>62</v>
@@ -55365,9 +55375,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>338</v>
+        <v>572</v>
       </c>
       <c r="B65" s="5">
         <v>63</v>
@@ -55376,9 +55386,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>339</v>
+        <v>573</v>
       </c>
       <c r="B66" s="5">
         <v>64</v>
@@ -55386,10 +55396,13 @@
       <c r="C66" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>340</v>
+        <v>574</v>
       </c>
       <c r="B67" s="5">
         <v>65</v>
@@ -55397,10 +55410,13 @@
       <c r="C67" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>341</v>
+        <v>575</v>
       </c>
       <c r="B68" s="5">
         <v>66</v>
@@ -55408,10 +55424,13 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>342</v>
+        <v>576</v>
       </c>
       <c r="B69" s="5">
         <v>67</v>
@@ -55419,10 +55438,13 @@
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>343</v>
+        <v>577</v>
       </c>
       <c r="B70" s="5">
         <v>68</v>
@@ -55430,10 +55452,13 @@
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>344</v>
+        <v>578</v>
       </c>
       <c r="B71" s="5">
         <v>69</v>
@@ -55442,9 +55467,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>345</v>
+        <v>579</v>
       </c>
       <c r="B72" s="5">
         <v>70</v>
@@ -55453,9 +55478,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>346</v>
+        <v>580</v>
       </c>
       <c r="B73" s="5">
         <v>71</v>
@@ -55464,9 +55489,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>347</v>
+        <v>581</v>
       </c>
       <c r="B74" s="5">
         <v>72</v>
@@ -55475,9 +55500,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>348</v>
+        <v>582</v>
       </c>
       <c r="B75" s="5">
         <v>73</v>
@@ -55486,9 +55511,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>349</v>
+        <v>583</v>
       </c>
       <c r="B76" s="5">
         <v>74</v>
@@ -55497,9 +55522,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>350</v>
+        <v>584</v>
       </c>
       <c r="B77" s="5">
         <v>75</v>
@@ -55508,9 +55533,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>351</v>
+        <v>585</v>
       </c>
       <c r="B78" s="5">
         <v>76</v>
@@ -55519,9 +55544,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>352</v>
+        <v>586</v>
       </c>
       <c r="B79" s="5">
         <v>77</v>
@@ -55530,9 +55555,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>353</v>
+        <v>587</v>
       </c>
       <c r="B80" s="5">
         <v>78</v>
@@ -55543,7 +55568,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>354</v>
+        <v>588</v>
       </c>
       <c r="B81" s="5">
         <v>79</v>
@@ -55554,7 +55579,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>355</v>
+        <v>589</v>
       </c>
       <c r="B82" s="5">
         <v>80</v>
@@ -55565,7 +55590,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>356</v>
+        <v>590</v>
       </c>
       <c r="B83" s="5">
         <v>81</v>
@@ -55576,7 +55601,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>357</v>
+        <v>591</v>
       </c>
       <c r="B84" s="5">
         <v>82</v>
@@ -55587,7 +55612,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>358</v>
+        <v>592</v>
       </c>
       <c r="B85" s="5">
         <v>83</v>
@@ -55598,7 +55623,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>359</v>
+        <v>593</v>
       </c>
       <c r="B86" s="5">
         <v>84</v>
@@ -55609,7 +55634,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>360</v>
+        <v>594</v>
       </c>
       <c r="B87" s="5">
         <v>85</v>
@@ -55620,7 +55645,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>361</v>
+        <v>595</v>
       </c>
       <c r="B88" s="5">
         <v>86</v>
@@ -55631,7 +55656,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>362</v>
+        <v>596</v>
       </c>
       <c r="B89" s="5">
         <v>87</v>
@@ -55642,7 +55667,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>363</v>
+        <v>597</v>
       </c>
       <c r="B90" s="5">
         <v>88</v>
@@ -55653,7 +55678,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>364</v>
+        <v>598</v>
       </c>
       <c r="B91" s="5">
         <v>89</v>
@@ -55664,7 +55689,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>365</v>
+        <v>599</v>
       </c>
       <c r="B92" s="5">
         <v>90</v>
@@ -55675,7 +55700,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>366</v>
+        <v>600</v>
       </c>
       <c r="B93" s="5">
         <v>91</v>
@@ -55686,7 +55711,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>367</v>
+        <v>601</v>
       </c>
       <c r="B94" s="5">
         <v>92</v>
@@ -55697,7 +55722,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>368</v>
+        <v>602</v>
       </c>
       <c r="B95" s="5">
         <v>93</v>
@@ -55708,7 +55733,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>369</v>
+        <v>603</v>
       </c>
       <c r="B96" s="5">
         <v>94</v>
@@ -55719,18 +55744,18 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>370</v>
+        <v>604</v>
       </c>
       <c r="B97" s="5">
         <v>95</v>
       </c>
       <c r="C97" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>371</v>
+        <v>605</v>
       </c>
       <c r="B98" s="5">
         <v>96</v>
@@ -55741,7 +55766,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>372</v>
+        <v>606</v>
       </c>
       <c r="B99" s="5">
         <v>97</v>
@@ -55752,7 +55777,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>373</v>
+        <v>607</v>
       </c>
       <c r="B100" s="5">
         <v>98</v>
@@ -55763,29 +55788,29 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>374</v>
+        <v>608</v>
       </c>
       <c r="B101" s="5">
         <v>99</v>
       </c>
       <c r="C101" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="B102" s="5">
         <v>100</v>
       </c>
       <c r="C102" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>376</v>
+        <v>276</v>
       </c>
       <c r="B103" s="5">
         <v>101</v>
@@ -55796,7 +55821,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>377</v>
+        <v>277</v>
       </c>
       <c r="B104" s="5">
         <v>102</v>
@@ -55807,7 +55832,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>378</v>
+        <v>278</v>
       </c>
       <c r="B105" s="5">
         <v>103</v>
@@ -55818,7 +55843,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>379</v>
+        <v>279</v>
       </c>
       <c r="B106" s="5">
         <v>104</v>
@@ -55829,29 +55854,29 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="B107" s="5">
         <v>105</v>
       </c>
       <c r="C107" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="B108" s="5">
         <v>106</v>
       </c>
       <c r="C108" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>382</v>
+        <v>282</v>
       </c>
       <c r="B109" s="5">
         <v>107</v>
@@ -55862,7 +55887,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>383</v>
+        <v>283</v>
       </c>
       <c r="B110" s="5">
         <v>108</v>
@@ -55873,7 +55898,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="B111" s="5">
         <v>109</v>
@@ -55884,7 +55909,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>385</v>
+        <v>285</v>
       </c>
       <c r="B112" s="5">
         <v>110</v>
@@ -55895,7 +55920,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>386</v>
+        <v>286</v>
       </c>
       <c r="B113" s="5">
         <v>111</v>
@@ -55906,7 +55931,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>387</v>
+        <v>287</v>
       </c>
       <c r="B114" s="5">
         <v>112</v>
@@ -55917,7 +55942,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>388</v>
+        <v>288</v>
       </c>
       <c r="B115" s="5">
         <v>113</v>
@@ -55928,7 +55953,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>389</v>
+        <v>289</v>
       </c>
       <c r="B116" s="5">
         <v>114</v>
@@ -55939,7 +55964,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>390</v>
+        <v>290</v>
       </c>
       <c r="B117" s="5">
         <v>115</v>
@@ -55950,7 +55975,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>391</v>
+        <v>291</v>
       </c>
       <c r="B118" s="5">
         <v>116</v>
@@ -55961,7 +55986,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>392</v>
+        <v>292</v>
       </c>
       <c r="B119" s="5">
         <v>117</v>
@@ -55972,7 +55997,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>393</v>
+        <v>293</v>
       </c>
       <c r="B120" s="5">
         <v>118</v>
@@ -55983,7 +56008,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>394</v>
+        <v>294</v>
       </c>
       <c r="B121" s="5">
         <v>119</v>
@@ -55994,7 +56019,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="B122" s="5">
         <v>120</v>
@@ -56005,7 +56030,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>396</v>
+        <v>296</v>
       </c>
       <c r="B123" s="5">
         <v>121</v>
@@ -56016,7 +56041,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>397</v>
+        <v>297</v>
       </c>
       <c r="B124" s="5">
         <v>122</v>
@@ -56027,7 +56052,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>398</v>
+        <v>298</v>
       </c>
       <c r="B125" s="5">
         <v>123</v>
@@ -56038,7 +56063,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="B126" s="5">
         <v>124</v>
@@ -56049,7 +56074,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B127" s="5">
         <v>125</v>
@@ -56060,7 +56085,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>401</v>
+        <v>301</v>
       </c>
       <c r="B128" s="5">
         <v>126</v>
@@ -56071,7 +56096,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>402</v>
+        <v>302</v>
       </c>
       <c r="B129" s="5">
         <v>127</v>
@@ -56082,7 +56107,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>403</v>
+        <v>303</v>
       </c>
       <c r="B130" s="5">
         <v>128</v>
@@ -56093,7 +56118,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>404</v>
+        <v>304</v>
       </c>
       <c r="B131" s="5">
         <v>129</v>
@@ -56104,7 +56129,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>405</v>
+        <v>305</v>
       </c>
       <c r="B132" s="5">
         <v>130</v>
@@ -56115,7 +56140,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>406</v>
+        <v>306</v>
       </c>
       <c r="B133" s="5">
         <v>131</v>
@@ -56126,7 +56151,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>407</v>
+        <v>307</v>
       </c>
       <c r="B134" s="5">
         <v>132</v>
@@ -56137,7 +56162,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>408</v>
+        <v>308</v>
       </c>
       <c r="B135" s="5">
         <v>133</v>
@@ -56148,7 +56173,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>309</v>
       </c>
       <c r="B136" s="5">
         <v>134</v>
@@ -56159,7 +56184,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>410</v>
+        <v>310</v>
       </c>
       <c r="B137" s="5">
         <v>135</v>
@@ -56170,7 +56195,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>411</v>
+        <v>311</v>
       </c>
       <c r="B138" s="5">
         <v>136</v>
@@ -56181,7 +56206,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>412</v>
+        <v>312</v>
       </c>
       <c r="B139" s="5">
         <v>137</v>
@@ -56192,7 +56217,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>413</v>
+        <v>313</v>
       </c>
       <c r="B140" s="5">
         <v>138</v>
@@ -56203,7 +56228,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>414</v>
+        <v>314</v>
       </c>
       <c r="B141" s="5">
         <v>139</v>
@@ -56214,7 +56239,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="B142" s="5">
         <v>140</v>
@@ -56225,7 +56250,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>416</v>
+        <v>316</v>
       </c>
       <c r="B143" s="5">
         <v>141</v>
@@ -56236,7 +56261,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>417</v>
+        <v>317</v>
       </c>
       <c r="B144" s="5">
         <v>142</v>
@@ -56247,18 +56272,18 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>418</v>
+        <v>318</v>
       </c>
       <c r="B145" s="5">
         <v>143</v>
       </c>
       <c r="C145" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>419</v>
+        <v>319</v>
       </c>
       <c r="B146" s="5">
         <v>144</v>
@@ -56269,7 +56294,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="B147" s="5">
         <v>145</v>
@@ -56280,7 +56305,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>421</v>
+        <v>321</v>
       </c>
       <c r="B148" s="5">
         <v>146</v>
@@ -56291,7 +56316,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>422</v>
+        <v>322</v>
       </c>
       <c r="B149" s="5">
         <v>147</v>
@@ -56302,7 +56327,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>423</v>
+        <v>323</v>
       </c>
       <c r="B150" s="5">
         <v>148</v>
@@ -56313,7 +56338,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>424</v>
+        <v>324</v>
       </c>
       <c r="B151" s="5">
         <v>149</v>
@@ -56324,7 +56349,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="B152" s="5">
         <v>150</v>
@@ -56335,7 +56360,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>426</v>
+        <v>326</v>
       </c>
       <c r="B153" s="5">
         <v>151</v>
@@ -56346,7 +56371,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>427</v>
+        <v>327</v>
       </c>
       <c r="B154" s="5">
         <v>152</v>
@@ -56357,7 +56382,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>428</v>
+        <v>328</v>
       </c>
       <c r="B155" s="5">
         <v>153</v>
@@ -56368,7 +56393,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="B156" s="5">
         <v>154</v>
@@ -56379,7 +56404,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>430</v>
+        <v>330</v>
       </c>
       <c r="B157" s="5">
         <v>155</v>
@@ -56390,7 +56415,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>431</v>
+        <v>331</v>
       </c>
       <c r="B158" s="5">
         <v>156</v>
@@ -56401,7 +56426,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>432</v>
+        <v>332</v>
       </c>
       <c r="B159" s="5">
         <v>157</v>
@@ -56412,7 +56437,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>433</v>
+        <v>333</v>
       </c>
       <c r="B160" s="5">
         <v>158</v>
@@ -56423,7 +56448,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>434</v>
+        <v>334</v>
       </c>
       <c r="B161" s="5">
         <v>159</v>
@@ -56434,7 +56459,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>435</v>
+        <v>335</v>
       </c>
       <c r="B162" s="5">
         <v>160</v>
@@ -56445,18 +56470,18 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>436</v>
+        <v>336</v>
       </c>
       <c r="B163" s="5">
         <v>161</v>
       </c>
       <c r="C163" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>437</v>
+        <v>337</v>
       </c>
       <c r="B164" s="5">
         <v>162</v>
@@ -56467,7 +56492,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>438</v>
+        <v>338</v>
       </c>
       <c r="B165" s="5">
         <v>163</v>
@@ -56478,7 +56503,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>439</v>
+        <v>339</v>
       </c>
       <c r="B166" s="5">
         <v>164</v>
@@ -56489,7 +56514,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="B167" s="5">
         <v>165</v>
@@ -56500,7 +56525,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>441</v>
+        <v>341</v>
       </c>
       <c r="B168" s="5">
         <v>166</v>
@@ -56511,7 +56536,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>442</v>
+        <v>342</v>
       </c>
       <c r="B169" s="5">
         <v>167</v>
@@ -56522,7 +56547,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>443</v>
+        <v>343</v>
       </c>
       <c r="B170" s="5">
         <v>168</v>
@@ -56533,7 +56558,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>444</v>
+        <v>344</v>
       </c>
       <c r="B171" s="5">
         <v>169</v>
@@ -56544,7 +56569,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>445</v>
+        <v>345</v>
       </c>
       <c r="B172" s="5">
         <v>170</v>
@@ -56555,7 +56580,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>446</v>
+        <v>346</v>
       </c>
       <c r="B173" s="5">
         <v>171</v>
@@ -56566,7 +56591,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>447</v>
+        <v>347</v>
       </c>
       <c r="B174" s="5">
         <v>172</v>
@@ -56577,7 +56602,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>448</v>
+        <v>348</v>
       </c>
       <c r="B175" s="5">
         <v>173</v>
@@ -56588,7 +56613,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>449</v>
+        <v>349</v>
       </c>
       <c r="B176" s="5">
         <v>174</v>
@@ -56599,7 +56624,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="B177" s="5">
         <v>175</v>
@@ -56610,18 +56635,18 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>451</v>
+        <v>351</v>
       </c>
       <c r="B178" s="5">
         <v>176</v>
       </c>
       <c r="C178" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>452</v>
+        <v>352</v>
       </c>
       <c r="B179" s="5">
         <v>177</v>
@@ -56632,7 +56657,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>453</v>
+        <v>353</v>
       </c>
       <c r="B180" s="5">
         <v>178</v>
@@ -56643,7 +56668,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>454</v>
+        <v>354</v>
       </c>
       <c r="B181" s="5">
         <v>179</v>
@@ -56654,7 +56679,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>455</v>
+        <v>355</v>
       </c>
       <c r="B182" s="5">
         <v>180</v>
@@ -56665,7 +56690,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>456</v>
+        <v>356</v>
       </c>
       <c r="B183" s="5">
         <v>181</v>
@@ -56676,7 +56701,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>457</v>
+        <v>357</v>
       </c>
       <c r="B184" s="5">
         <v>182</v>
@@ -56687,7 +56712,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>458</v>
+        <v>358</v>
       </c>
       <c r="B185" s="5">
         <v>183</v>
@@ -56698,7 +56723,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>459</v>
+        <v>359</v>
       </c>
       <c r="B186" s="5">
         <v>184</v>
@@ -56709,7 +56734,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>460</v>
+        <v>360</v>
       </c>
       <c r="B187" s="5">
         <v>185</v>
@@ -56720,7 +56745,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>461</v>
+        <v>361</v>
       </c>
       <c r="B188" s="5">
         <v>186</v>
@@ -56731,7 +56756,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>462</v>
+        <v>362</v>
       </c>
       <c r="B189" s="5">
         <v>187</v>
@@ -56742,7 +56767,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>463</v>
+        <v>363</v>
       </c>
       <c r="B190" s="5">
         <v>188</v>
@@ -56753,7 +56778,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>464</v>
+        <v>364</v>
       </c>
       <c r="B191" s="5">
         <v>189</v>
@@ -56764,18 +56789,18 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>465</v>
+        <v>365</v>
       </c>
       <c r="B192" s="5">
         <v>190</v>
       </c>
       <c r="C192" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>466</v>
+        <v>366</v>
       </c>
       <c r="B193" s="5">
         <v>191</v>
@@ -56786,7 +56811,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>467</v>
+        <v>367</v>
       </c>
       <c r="B194" s="5">
         <v>192</v>
@@ -56797,7 +56822,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>468</v>
+        <v>368</v>
       </c>
       <c r="B195" s="5">
         <v>193</v>
@@ -56808,7 +56833,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>469</v>
+        <v>369</v>
       </c>
       <c r="B196" s="5">
         <v>194</v>
@@ -56819,7 +56844,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>470</v>
+        <v>370</v>
       </c>
       <c r="B197" s="5">
         <v>195</v>
@@ -56830,7 +56855,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>471</v>
+        <v>371</v>
       </c>
       <c r="B198" s="5">
         <v>196</v>
@@ -56841,29 +56866,29 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>472</v>
+        <v>372</v>
       </c>
       <c r="B199" s="5">
         <v>197</v>
       </c>
       <c r="C199" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>473</v>
+        <v>373</v>
       </c>
       <c r="B200" s="5">
         <v>198</v>
       </c>
       <c r="C200" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="B201" s="5">
         <v>199</v>
@@ -56874,7 +56899,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="B202" s="5">
         <v>200</v>
@@ -56885,7 +56910,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>476</v>
+        <v>376</v>
       </c>
       <c r="B203" s="5">
         <v>201</v>
@@ -56896,18 +56921,18 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>477</v>
+        <v>377</v>
       </c>
       <c r="B204" s="5">
         <v>202</v>
       </c>
       <c r="C204" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>478</v>
+        <v>378</v>
       </c>
       <c r="B205" s="5">
         <v>203</v>
@@ -56918,18 +56943,18 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>479</v>
+        <v>379</v>
       </c>
       <c r="B206" s="5">
         <v>204</v>
       </c>
       <c r="C206" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="B207" s="5">
         <v>205</v>
@@ -56940,29 +56965,29 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>481</v>
+        <v>381</v>
       </c>
       <c r="B208" s="5">
         <v>206</v>
       </c>
       <c r="C208" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>482</v>
+        <v>382</v>
       </c>
       <c r="B209" s="5">
         <v>207</v>
       </c>
       <c r="C209" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>483</v>
+        <v>383</v>
       </c>
       <c r="B210" s="5">
         <v>208</v>
@@ -56973,7 +56998,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>484</v>
+        <v>384</v>
       </c>
       <c r="B211" s="5">
         <v>209</v>
@@ -56984,7 +57009,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
       <c r="B212" s="5">
         <v>210</v>
@@ -56995,7 +57020,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>486</v>
+        <v>386</v>
       </c>
       <c r="B213" s="5">
         <v>211</v>
@@ -57006,7 +57031,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>487</v>
+        <v>387</v>
       </c>
       <c r="B214" s="5">
         <v>212</v>
@@ -57017,7 +57042,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>488</v>
+        <v>388</v>
       </c>
       <c r="B215" s="5">
         <v>213</v>
@@ -57028,7 +57053,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>489</v>
+        <v>389</v>
       </c>
       <c r="B216" s="5">
         <v>214</v>
@@ -57039,7 +57064,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>490</v>
+        <v>390</v>
       </c>
       <c r="B217" s="5">
         <v>215</v>
@@ -57048,20 +57073,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>491</v>
+        <v>391</v>
       </c>
       <c r="B218" s="5">
         <v>216</v>
       </c>
-      <c r="C218" s="1" t="b">
-        <v>1</v>
+      <c r="C218" s="6" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>492</v>
+        <v>392</v>
       </c>
       <c r="B219" s="5">
         <v>217</v>
@@ -57072,7 +57097,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>493</v>
+        <v>393</v>
       </c>
       <c r="B220" s="5">
         <v>218</v>
@@ -57083,7 +57108,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>494</v>
+        <v>394</v>
       </c>
       <c r="B221" s="5">
         <v>219</v>
@@ -57094,7 +57119,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>495</v>
+        <v>395</v>
       </c>
       <c r="B222" s="5">
         <v>220</v>
@@ -57105,7 +57130,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>496</v>
+        <v>396</v>
       </c>
       <c r="B223" s="5">
         <v>221</v>
@@ -57116,7 +57141,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>497</v>
+        <v>397</v>
       </c>
       <c r="B224" s="5">
         <v>222</v>
@@ -57127,7 +57152,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>498</v>
+        <v>398</v>
       </c>
       <c r="B225" s="5">
         <v>223</v>
@@ -57138,7 +57163,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="B226" s="5">
         <v>224</v>
@@ -57149,7 +57174,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="B227" s="5">
         <v>225</v>
@@ -57160,7 +57185,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>501</v>
+        <v>401</v>
       </c>
       <c r="B228" s="5">
         <v>226</v>
@@ -57171,7 +57196,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>502</v>
+        <v>402</v>
       </c>
       <c r="B229" s="5">
         <v>227</v>
@@ -57182,7 +57207,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>503</v>
+        <v>403</v>
       </c>
       <c r="B230" s="5">
         <v>228</v>
@@ -57193,7 +57218,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>504</v>
+        <v>404</v>
       </c>
       <c r="B231" s="5">
         <v>229</v>
@@ -57204,7 +57229,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>505</v>
+        <v>405</v>
       </c>
       <c r="B232" s="5">
         <v>230</v>
@@ -57215,7 +57240,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>506</v>
+        <v>406</v>
       </c>
       <c r="B233" s="5">
         <v>231</v>
@@ -57226,7 +57251,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>507</v>
+        <v>407</v>
       </c>
       <c r="B234" s="5">
         <v>232</v>
@@ -57237,7 +57262,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>508</v>
+        <v>408</v>
       </c>
       <c r="B235" s="5">
         <v>233</v>
@@ -57248,7 +57273,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>509</v>
+        <v>409</v>
       </c>
       <c r="B236" s="5">
         <v>234</v>
@@ -57259,7 +57284,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="B237" s="5">
         <v>235</v>
@@ -57270,7 +57295,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>511</v>
+        <v>411</v>
       </c>
       <c r="B238" s="5">
         <v>236</v>
@@ -57281,7 +57306,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>512</v>
+        <v>412</v>
       </c>
       <c r="B239" s="5">
         <v>237</v>
@@ -57292,7 +57317,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>513</v>
+        <v>413</v>
       </c>
       <c r="B240" s="5">
         <v>238</v>
@@ -57303,7 +57328,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>514</v>
+        <v>414</v>
       </c>
       <c r="B241" s="5">
         <v>239</v>
@@ -57314,7 +57339,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>515</v>
+        <v>415</v>
       </c>
       <c r="B242" s="5">
         <v>240</v>
@@ -57325,7 +57350,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>516</v>
+        <v>416</v>
       </c>
       <c r="B243" s="5">
         <v>241</v>
@@ -57336,7 +57361,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>517</v>
+        <v>417</v>
       </c>
       <c r="B244" s="5">
         <v>242</v>
@@ -57347,7 +57372,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>518</v>
+        <v>418</v>
       </c>
       <c r="B245" s="5">
         <v>243</v>
@@ -57358,40 +57383,40 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>519</v>
+        <v>419</v>
       </c>
       <c r="B246" s="5">
         <v>244</v>
       </c>
       <c r="C246" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="B247" s="5">
         <v>245</v>
       </c>
       <c r="C247" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>521</v>
+        <v>421</v>
       </c>
       <c r="B248" s="5">
         <v>246</v>
       </c>
       <c r="C248" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>522</v>
+        <v>422</v>
       </c>
       <c r="B249" s="5">
         <v>247</v>
@@ -57402,7 +57427,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>523</v>
+        <v>423</v>
       </c>
       <c r="B250" s="5">
         <v>248</v>
@@ -57413,29 +57438,29 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>524</v>
+        <v>424</v>
       </c>
       <c r="B251" s="5">
         <v>249</v>
       </c>
       <c r="C251" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>525</v>
+        <v>425</v>
       </c>
       <c r="B252" s="5">
         <v>250</v>
       </c>
       <c r="C252" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>526</v>
+        <v>426</v>
       </c>
       <c r="B253" s="5">
         <v>251</v>
@@ -57446,7 +57471,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>527</v>
+        <v>427</v>
       </c>
       <c r="B254" s="5">
         <v>252</v>
@@ -57457,40 +57482,40 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>528</v>
+        <v>428</v>
       </c>
       <c r="B255" s="5">
         <v>253</v>
       </c>
       <c r="C255" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>529</v>
+        <v>429</v>
       </c>
       <c r="B256" s="5">
         <v>254</v>
       </c>
       <c r="C256" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>530</v>
+        <v>430</v>
       </c>
       <c r="B257" s="5">
         <v>255</v>
       </c>
       <c r="C257" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>531</v>
+        <v>431</v>
       </c>
       <c r="B258" s="5">
         <v>256</v>
@@ -57501,7 +57526,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>532</v>
+        <v>432</v>
       </c>
       <c r="B259" s="5">
         <v>257</v>
@@ -57512,7 +57537,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>533</v>
+        <v>433</v>
       </c>
       <c r="B260" s="5">
         <v>258</v>
@@ -57523,7 +57548,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>534</v>
+        <v>434</v>
       </c>
       <c r="B261" s="5">
         <v>259</v>
@@ -57534,18 +57559,18 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>535</v>
+        <v>435</v>
       </c>
       <c r="B262" s="5">
         <v>260</v>
       </c>
       <c r="C262" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>536</v>
+        <v>436</v>
       </c>
       <c r="B263" s="5">
         <v>261</v>
@@ -57556,7 +57581,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>537</v>
+        <v>437</v>
       </c>
       <c r="B264" s="5">
         <v>262</v>
@@ -57567,7 +57592,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>538</v>
+        <v>438</v>
       </c>
       <c r="B265" s="5">
         <v>263</v>
@@ -57578,7 +57603,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>539</v>
+        <v>439</v>
       </c>
       <c r="B266" s="5">
         <v>264</v>
@@ -57589,18 +57614,18 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>540</v>
+        <v>440</v>
       </c>
       <c r="B267" s="5">
         <v>265</v>
       </c>
       <c r="C267" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>541</v>
+        <v>441</v>
       </c>
       <c r="B268" s="5">
         <v>266</v>
@@ -57611,29 +57636,29 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>542</v>
+        <v>442</v>
       </c>
       <c r="B269" s="5">
         <v>267</v>
       </c>
       <c r="C269" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>543</v>
+        <v>443</v>
       </c>
       <c r="B270" s="5">
         <v>268</v>
       </c>
       <c r="C270" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>544</v>
+        <v>444</v>
       </c>
       <c r="B271" s="5">
         <v>269</v>
@@ -57644,7 +57669,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>545</v>
+        <v>445</v>
       </c>
       <c r="B272" s="5">
         <v>270</v>
@@ -57655,7 +57680,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>546</v>
+        <v>446</v>
       </c>
       <c r="B273" s="5">
         <v>271</v>
@@ -57666,7 +57691,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>547</v>
+        <v>447</v>
       </c>
       <c r="B274" s="5">
         <v>272</v>
@@ -57677,7 +57702,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>548</v>
+        <v>448</v>
       </c>
       <c r="B275" s="5">
         <v>273</v>
@@ -57688,7 +57713,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>549</v>
+        <v>449</v>
       </c>
       <c r="B276" s="5">
         <v>274</v>
@@ -57699,7 +57724,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="B277" s="5">
         <v>275</v>
@@ -57710,7 +57735,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>551</v>
+        <v>451</v>
       </c>
       <c r="B278" s="5">
         <v>276</v>
@@ -57721,7 +57746,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>552</v>
+        <v>452</v>
       </c>
       <c r="B279" s="5">
         <v>277</v>
@@ -57732,7 +57757,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>553</v>
+        <v>453</v>
       </c>
       <c r="B280" s="5">
         <v>278</v>
@@ -57743,7 +57768,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>554</v>
+        <v>454</v>
       </c>
       <c r="B281" s="5">
         <v>279</v>
@@ -57754,7 +57779,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>555</v>
+        <v>455</v>
       </c>
       <c r="B282" s="5">
         <v>280</v>
@@ -57765,7 +57790,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>556</v>
+        <v>456</v>
       </c>
       <c r="B283" s="5">
         <v>281</v>
@@ -57776,7 +57801,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>557</v>
+        <v>457</v>
       </c>
       <c r="B284" s="5">
         <v>282</v>
@@ -57787,18 +57812,18 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>558</v>
+        <v>458</v>
       </c>
       <c r="B285" s="5">
         <v>283</v>
       </c>
       <c r="C285" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>559</v>
+        <v>459</v>
       </c>
       <c r="B286" s="5">
         <v>284</v>
@@ -57809,7 +57834,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="B287" s="5">
         <v>285</v>
@@ -57818,20 +57843,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>561</v>
+        <v>461</v>
       </c>
       <c r="B288" s="5">
         <v>286</v>
       </c>
-      <c r="C288" s="1" t="b">
-        <v>1</v>
+      <c r="C288" s="6" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>562</v>
+        <v>462</v>
       </c>
       <c r="B289" s="5">
         <v>287</v>
@@ -57842,18 +57867,18 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>563</v>
+        <v>463</v>
       </c>
       <c r="B290" s="5">
         <v>288</v>
       </c>
       <c r="C290" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>564</v>
+        <v>464</v>
       </c>
       <c r="B291" s="5">
         <v>289</v>
@@ -57864,7 +57889,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>565</v>
+        <v>465</v>
       </c>
       <c r="B292" s="5">
         <v>290</v>
@@ -57875,7 +57900,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>566</v>
+        <v>466</v>
       </c>
       <c r="B293" s="5">
         <v>291</v>
@@ -57886,7 +57911,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>567</v>
+        <v>467</v>
       </c>
       <c r="B294" s="5">
         <v>292</v>
@@ -57897,7 +57922,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>568</v>
+        <v>468</v>
       </c>
       <c r="B295" s="5">
         <v>293</v>
@@ -57908,7 +57933,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>569</v>
+        <v>469</v>
       </c>
       <c r="B296" s="5">
         <v>294</v>
@@ -57919,7 +57944,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="B297" s="5">
         <v>295</v>
@@ -57930,7 +57955,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>571</v>
+        <v>471</v>
       </c>
       <c r="B298" s="5">
         <v>296</v>
@@ -57941,29 +57966,29 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>572</v>
+        <v>472</v>
       </c>
       <c r="B299" s="5">
         <v>297</v>
       </c>
       <c r="C299" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>573</v>
+        <v>473</v>
       </c>
       <c r="B300" s="5">
         <v>298</v>
       </c>
       <c r="C300" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>574</v>
+        <v>474</v>
       </c>
       <c r="B301" s="5">
         <v>299</v>
@@ -57972,9 +57997,9 @@
         <v>274</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>575</v>
+        <v>475</v>
       </c>
       <c r="B302" s="5">
         <v>300</v>
@@ -57985,7 +58010,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>576</v>
+        <v>476</v>
       </c>
       <c r="B303" s="5">
         <v>301</v>
@@ -57996,7 +58021,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>577</v>
+        <v>477</v>
       </c>
       <c r="B304" s="5">
         <v>302</v>
@@ -58007,7 +58032,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>578</v>
+        <v>478</v>
       </c>
       <c r="B305" s="5">
         <v>303</v>
@@ -58018,7 +58043,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>579</v>
+        <v>479</v>
       </c>
       <c r="B306" s="5">
         <v>304</v>
@@ -58029,7 +58054,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="B307" s="5">
         <v>305</v>
@@ -58040,7 +58065,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>581</v>
+        <v>481</v>
       </c>
       <c r="B308" s="5">
         <v>306</v>
@@ -58051,7 +58076,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>582</v>
+        <v>482</v>
       </c>
       <c r="B309" s="5">
         <v>307</v>
@@ -58062,7 +58087,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>583</v>
+        <v>483</v>
       </c>
       <c r="B310" s="5">
         <v>308</v>
@@ -58073,7 +58098,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>584</v>
+        <v>484</v>
       </c>
       <c r="B311" s="5">
         <v>309</v>
@@ -58084,18 +58109,18 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>585</v>
+        <v>485</v>
       </c>
       <c r="B312" s="5">
         <v>310</v>
       </c>
       <c r="C312" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>586</v>
+        <v>486</v>
       </c>
       <c r="B313" s="5">
         <v>311</v>
@@ -58106,7 +58131,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>587</v>
+        <v>487</v>
       </c>
       <c r="B314" s="5">
         <v>312</v>
@@ -58117,7 +58142,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>588</v>
+        <v>488</v>
       </c>
       <c r="B315" s="5">
         <v>313</v>
@@ -58128,7 +58153,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>589</v>
+        <v>489</v>
       </c>
       <c r="B316" s="5">
         <v>314</v>
@@ -58139,7 +58164,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="B317" s="5">
         <v>315</v>
@@ -58150,7 +58175,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>591</v>
+        <v>491</v>
       </c>
       <c r="B318" s="5">
         <v>316</v>
@@ -58161,7 +58186,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>592</v>
+        <v>492</v>
       </c>
       <c r="B319" s="5">
         <v>317</v>
@@ -58172,7 +58197,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>593</v>
+        <v>493</v>
       </c>
       <c r="B320" s="5">
         <v>318</v>
@@ -58183,29 +58208,29 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>594</v>
+        <v>494</v>
       </c>
       <c r="B321" s="5">
         <v>319</v>
       </c>
       <c r="C321" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>595</v>
+        <v>495</v>
       </c>
       <c r="B322" s="5">
         <v>320</v>
       </c>
       <c r="C322" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>596</v>
+        <v>496</v>
       </c>
       <c r="B323" s="5">
         <v>321</v>
@@ -58216,29 +58241,29 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>597</v>
+        <v>497</v>
       </c>
       <c r="B324" s="5">
         <v>322</v>
       </c>
       <c r="C324" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>598</v>
+        <v>498</v>
       </c>
       <c r="B325" s="5">
         <v>323</v>
       </c>
       <c r="C325" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="B326" s="5">
         <v>324</v>
@@ -58247,9 +58272,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>600</v>
+        <v>499</v>
       </c>
       <c r="B327" s="5">
         <v>325</v>
@@ -58260,83 +58285,90 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>601</v>
+        <v>500</v>
       </c>
       <c r="B328" s="5">
         <v>326</v>
       </c>
       <c r="C328" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>602</v>
+        <v>501</v>
       </c>
       <c r="B329" s="5">
         <v>327</v>
       </c>
       <c r="C329" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>603</v>
+        <v>502</v>
       </c>
       <c r="B330" s="5">
         <v>328</v>
       </c>
       <c r="C330" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>604</v>
+        <v>503</v>
       </c>
       <c r="B331" s="5">
         <v>329</v>
       </c>
       <c r="C331" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>605</v>
+        <v>504</v>
       </c>
       <c r="B332" s="4">
         <v>330</v>
       </c>
       <c r="C332" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>606</v>
+        <v>505</v>
       </c>
       <c r="B333" s="4">
         <v>331</v>
       </c>
       <c r="C333" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>607</v>
+        <v>506</v>
       </c>
       <c r="B334" s="4">
         <v>332</v>
       </c>
       <c r="C334" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C331" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}"/>
+  <autoFilter ref="A1:C334" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="FALSE"/>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="C2:C334">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>TRUE</formula>

--- a/Snobol Functions.xlsx
+++ b/Snobol Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcooper\source\repos\Spitbol4Win\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9999EBB-0BFF-46B9-9F9A-5957E27CCFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B816028-3588-41C1-BEFD-51FC8E6DB92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29604" yWindow="5004" windowWidth="19860" windowHeight="18816" activeTab="2" xr2:uid="{14808CA3-9D70-46D1-8654-4F03110B5BF1}"/>
+    <workbookView xWindow="30324" yWindow="4956" windowWidth="13416" windowHeight="18816" activeTab="2" xr2:uid="{14808CA3-9D70-46D1-8654-4F03110B5BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Keywords" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Errors" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Errors!$A$1:$C$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Errors!$A$1:$C$335</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Keywords!$A$1:$D$16631</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Testing!$A$1:$C$135</definedName>
   </definedNames>
@@ -42,6 +42,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="611">
   <si>
@@ -1875,7 +1897,7 @@
     <t>324     set second argument not numeric (NOT FIRED)</t>
   </si>
   <si>
-    <t>testing</t>
+    <t>UNREACHABLE</t>
   </si>
 </sst>
 </file>
@@ -54663,12 +54685,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:M335"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="4"/>
-    <col min="3" max="3" width="12.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -54689,7 +54711,7 @@
       <c r="B2" s="5">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="b">
+      <c r="C2" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54700,7 +54722,7 @@
       <c r="B3" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="b">
+      <c r="C3" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54711,7 +54733,7 @@
       <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="b">
+      <c r="C4" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54722,7 +54744,7 @@
       <c r="B5" s="5">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="b">
+      <c r="C5" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54733,7 +54755,7 @@
       <c r="B6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="b">
+      <c r="C6" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54744,7 +54766,7 @@
       <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="b">
+      <c r="C7" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54755,19 +54777,19 @@
       <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="b">
+      <c r="C8" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>516</v>
       </c>
       <c r="B9" s="5">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="b">
-        <v>0</v>
+      <c r="C9" s="6" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -54777,7 +54799,7 @@
       <c r="B10" s="5">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="b">
+      <c r="C10" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54788,7 +54810,7 @@
       <c r="B11" s="5">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="b">
+      <c r="C11" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54799,7 +54821,7 @@
       <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="1" t="b">
+      <c r="C12" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54810,7 +54832,7 @@
       <c r="B13" s="5">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="b">
+      <c r="C13" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54821,7 +54843,7 @@
       <c r="B14" s="5">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="b">
+      <c r="C14" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54832,7 +54854,7 @@
       <c r="B15" s="5">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="b">
+      <c r="C15" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54843,7 +54865,7 @@
       <c r="B16" s="5">
         <v>14</v>
       </c>
-      <c r="C16" s="1" t="b">
+      <c r="C16" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54854,7 +54876,7 @@
       <c r="B17" s="5">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="b">
+      <c r="C17" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54865,7 +54887,7 @@
       <c r="B18" s="5">
         <v>16</v>
       </c>
-      <c r="C18" s="1" t="b">
+      <c r="C18" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54876,7 +54898,7 @@
       <c r="B19" s="5">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="b">
+      <c r="C19" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54887,7 +54909,7 @@
       <c r="B20" s="5">
         <v>18</v>
       </c>
-      <c r="C20" s="1" t="b">
+      <c r="C20" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54909,7 +54931,7 @@
       <c r="B22" s="5">
         <v>20</v>
       </c>
-      <c r="C22" s="1" t="b">
+      <c r="C22" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54920,7 +54942,7 @@
       <c r="B23" s="5">
         <v>21</v>
       </c>
-      <c r="C23" s="1" t="b">
+      <c r="C23" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54931,7 +54953,7 @@
       <c r="B24" s="5">
         <v>22</v>
       </c>
-      <c r="C24" s="1" t="b">
+      <c r="C24" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54942,7 +54964,7 @@
       <c r="B25" s="5">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="b">
+      <c r="C25" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54953,7 +54975,7 @@
       <c r="B26" s="5">
         <v>24</v>
       </c>
-      <c r="C26" s="1" t="b">
+      <c r="C26" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54964,7 +54986,7 @@
       <c r="B27" s="5">
         <v>25</v>
       </c>
-      <c r="C27" s="1" t="b">
+      <c r="C27" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54975,7 +54997,7 @@
       <c r="B28" s="5">
         <v>26</v>
       </c>
-      <c r="C28" s="1" t="b">
+      <c r="C28" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54986,7 +55008,7 @@
       <c r="B29" s="5">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="b">
+      <c r="C29" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -54997,7 +55019,7 @@
       <c r="B30" s="5">
         <v>28</v>
       </c>
-      <c r="C30" s="1" t="b">
+      <c r="C30" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55008,7 +55030,7 @@
       <c r="B31" s="5">
         <v>29</v>
       </c>
-      <c r="C31" s="1" t="b">
+      <c r="C31" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55019,7 +55041,7 @@
       <c r="B32" s="5">
         <v>30</v>
       </c>
-      <c r="C32" s="1" t="b">
+      <c r="C32" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55030,7 +55052,7 @@
       <c r="B33" s="5">
         <v>31</v>
       </c>
-      <c r="C33" s="1" t="b">
+      <c r="C33" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55041,7 +55063,7 @@
       <c r="B34" s="5">
         <v>32</v>
       </c>
-      <c r="C34" s="1" t="b">
+      <c r="C34" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55052,7 +55074,7 @@
       <c r="B35" s="5">
         <v>33</v>
       </c>
-      <c r="C35" s="1" t="b">
+      <c r="C35" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55063,7 +55085,7 @@
       <c r="B36" s="5">
         <v>34</v>
       </c>
-      <c r="C36" s="1" t="b">
+      <c r="C36" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55074,7 +55096,7 @@
       <c r="B37" s="5">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="b">
+      <c r="C37" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55085,7 +55107,7 @@
       <c r="B38" s="5">
         <v>36</v>
       </c>
-      <c r="C38" s="1" t="b">
+      <c r="C38" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55096,7 +55118,7 @@
       <c r="B39" s="5">
         <v>37</v>
       </c>
-      <c r="C39" s="1" t="b">
+      <c r="C39" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55107,7 +55129,7 @@
       <c r="B40" s="5">
         <v>38</v>
       </c>
-      <c r="C40" s="1" t="b">
+      <c r="C40" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55118,7 +55140,7 @@
       <c r="B41" s="5">
         <v>39</v>
       </c>
-      <c r="C41" s="1" t="b">
+      <c r="C41" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -55129,7 +55151,7 @@
       <c r="B42" s="5">
         <v>40</v>
       </c>
-      <c r="C42" s="1" t="b">
+      <c r="C42" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -55140,7 +55162,7 @@
       <c r="B43" s="5">
         <v>41</v>
       </c>
-      <c r="C43" s="1" t="b">
+      <c r="C43" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55151,7 +55173,7 @@
       <c r="B44" s="5">
         <v>42</v>
       </c>
-      <c r="C44" s="1" t="b">
+      <c r="C44" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -55162,7 +55184,7 @@
       <c r="B45" s="5">
         <v>43</v>
       </c>
-      <c r="C45" s="1" t="b">
+      <c r="C45" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55173,7 +55195,7 @@
       <c r="B46" s="5">
         <v>44</v>
       </c>
-      <c r="C46" s="1" t="b">
+      <c r="C46" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55184,7 +55206,7 @@
       <c r="B47" s="5">
         <v>45</v>
       </c>
-      <c r="C47" s="1" t="b">
+      <c r="C47" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55195,7 +55217,7 @@
       <c r="B48" s="5">
         <v>46</v>
       </c>
-      <c r="C48" s="1" t="b">
+      <c r="C48" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55206,7 +55228,7 @@
       <c r="B49" s="5">
         <v>47</v>
       </c>
-      <c r="C49" s="1" t="b">
+      <c r="C49" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55217,7 +55239,7 @@
       <c r="B50" s="5">
         <v>48</v>
       </c>
-      <c r="C50" s="1" t="b">
+      <c r="C50" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55228,7 +55250,7 @@
       <c r="B51" s="5">
         <v>49</v>
       </c>
-      <c r="C51" s="1" t="b">
+      <c r="C51" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55239,7 +55261,7 @@
       <c r="B52" s="5">
         <v>50</v>
       </c>
-      <c r="C52" s="1" t="b">
+      <c r="C52" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55250,7 +55272,7 @@
       <c r="B53" s="5">
         <v>51</v>
       </c>
-      <c r="C53" s="1" t="b">
+      <c r="C53" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55261,7 +55283,7 @@
       <c r="B54" s="5">
         <v>52</v>
       </c>
-      <c r="C54" s="1" t="b">
+      <c r="C54" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55272,7 +55294,7 @@
       <c r="B55" s="5">
         <v>53</v>
       </c>
-      <c r="C55" s="1" t="b">
+      <c r="C55" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55283,7 +55305,7 @@
       <c r="B56" s="5">
         <v>54</v>
       </c>
-      <c r="C56" s="1" t="b">
+      <c r="C56" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55294,7 +55316,7 @@
       <c r="B57" s="5">
         <v>55</v>
       </c>
-      <c r="C57" s="1" t="b">
+      <c r="C57" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55305,7 +55327,7 @@
       <c r="B58" s="5">
         <v>56</v>
       </c>
-      <c r="C58" s="1" t="b">
+      <c r="C58" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55316,7 +55338,7 @@
       <c r="B59" s="5">
         <v>57</v>
       </c>
-      <c r="C59" s="1" t="b">
+      <c r="C59" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55327,7 +55349,7 @@
       <c r="B60" s="5">
         <v>58</v>
       </c>
-      <c r="C60" s="1" t="b">
+      <c r="C60" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55338,7 +55360,7 @@
       <c r="B61" s="5">
         <v>59</v>
       </c>
-      <c r="C61" s="1" t="b">
+      <c r="C61" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55349,7 +55371,7 @@
       <c r="B62" s="5">
         <v>60</v>
       </c>
-      <c r="C62" s="1" t="b">
+      <c r="C62" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55360,7 +55382,7 @@
       <c r="B63" s="5">
         <v>61</v>
       </c>
-      <c r="C63" s="1" t="b">
+      <c r="C63" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55371,198 +55393,183 @@
       <c r="B64" s="5">
         <v>62</v>
       </c>
-      <c r="C64" s="1" t="b">
+      <c r="C64" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>572</v>
       </c>
       <c r="B65" s="5">
         <v>63</v>
       </c>
-      <c r="C65" s="1" t="b">
+      <c r="C65" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>573</v>
       </c>
       <c r="B66" s="5">
         <v>64</v>
       </c>
-      <c r="C66" s="1" t="b">
+      <c r="C66" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="D66" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>574</v>
       </c>
       <c r="B67" s="5">
         <v>65</v>
       </c>
-      <c r="C67" s="1" t="b">
+      <c r="C67" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="D67" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>575</v>
       </c>
       <c r="B68" s="5">
         <v>66</v>
       </c>
-      <c r="C68" s="1" t="b">
+      <c r="C68" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="D68" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>576</v>
       </c>
       <c r="B69" s="5">
         <v>67</v>
       </c>
-      <c r="C69" s="1" t="b">
+      <c r="C69" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="D69" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>577</v>
       </c>
       <c r="B70" s="5">
         <v>68</v>
       </c>
-      <c r="C70" s="1" t="b">
+      <c r="C70" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="D70" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>578</v>
       </c>
       <c r="B71" s="5">
         <v>69</v>
       </c>
-      <c r="C71" s="1" t="b">
+      <c r="C71" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>579</v>
       </c>
       <c r="B72" s="5">
         <v>70</v>
       </c>
-      <c r="C72" s="1" t="b">
+      <c r="C72" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>580</v>
       </c>
       <c r="B73" s="5">
         <v>71</v>
       </c>
-      <c r="C73" s="1" t="b">
+      <c r="C73" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>581</v>
       </c>
       <c r="B74" s="5">
         <v>72</v>
       </c>
-      <c r="C74" s="1" t="b">
+      <c r="C74" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>582</v>
       </c>
       <c r="B75" s="5">
         <v>73</v>
       </c>
-      <c r="C75" s="1" t="b">
+      <c r="C75" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>583</v>
       </c>
       <c r="B76" s="5">
         <v>74</v>
       </c>
-      <c r="C76" s="1" t="b">
+      <c r="C76" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>584</v>
       </c>
       <c r="B77" s="5">
         <v>75</v>
       </c>
-      <c r="C77" s="1" t="b">
+      <c r="C77" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>585</v>
       </c>
       <c r="B78" s="5">
         <v>76</v>
       </c>
-      <c r="C78" s="1" t="b">
+      <c r="C78" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>586</v>
       </c>
       <c r="B79" s="5">
         <v>77</v>
       </c>
-      <c r="C79" s="1" t="b">
+      <c r="C79" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>587</v>
       </c>
       <c r="B80" s="5">
         <v>78</v>
       </c>
-      <c r="C80" s="1" t="b">
+      <c r="C80" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55573,7 +55580,7 @@
       <c r="B81" s="5">
         <v>79</v>
       </c>
-      <c r="C81" s="1" t="b">
+      <c r="C81" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55584,7 +55591,7 @@
       <c r="B82" s="5">
         <v>80</v>
       </c>
-      <c r="C82" s="1" t="b">
+      <c r="C82" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55595,7 +55602,7 @@
       <c r="B83" s="5">
         <v>81</v>
       </c>
-      <c r="C83" s="1" t="b">
+      <c r="C83" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55606,7 +55613,7 @@
       <c r="B84" s="5">
         <v>82</v>
       </c>
-      <c r="C84" s="1" t="b">
+      <c r="C84" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55617,7 +55624,7 @@
       <c r="B85" s="5">
         <v>83</v>
       </c>
-      <c r="C85" s="1" t="b">
+      <c r="C85" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55628,7 +55635,7 @@
       <c r="B86" s="5">
         <v>84</v>
       </c>
-      <c r="C86" s="1" t="b">
+      <c r="C86" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55639,7 +55646,7 @@
       <c r="B87" s="5">
         <v>85</v>
       </c>
-      <c r="C87" s="1" t="b">
+      <c r="C87" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55650,7 +55657,7 @@
       <c r="B88" s="5">
         <v>86</v>
       </c>
-      <c r="C88" s="1" t="b">
+      <c r="C88" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55661,7 +55668,7 @@
       <c r="B89" s="5">
         <v>87</v>
       </c>
-      <c r="C89" s="1" t="b">
+      <c r="C89" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55672,7 +55679,7 @@
       <c r="B90" s="5">
         <v>88</v>
       </c>
-      <c r="C90" s="1" t="b">
+      <c r="C90" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55683,7 +55690,7 @@
       <c r="B91" s="5">
         <v>89</v>
       </c>
-      <c r="C91" s="1" t="b">
+      <c r="C91" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55694,7 +55701,7 @@
       <c r="B92" s="5">
         <v>90</v>
       </c>
-      <c r="C92" s="1" t="b">
+      <c r="C92" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55705,7 +55712,7 @@
       <c r="B93" s="5">
         <v>91</v>
       </c>
-      <c r="C93" s="1" t="b">
+      <c r="C93" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55716,7 +55723,7 @@
       <c r="B94" s="5">
         <v>92</v>
       </c>
-      <c r="C94" s="1" t="b">
+      <c r="C94" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55727,7 +55734,7 @@
       <c r="B95" s="5">
         <v>93</v>
       </c>
-      <c r="C95" s="1" t="b">
+      <c r="C95" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55738,183 +55745,187 @@
       <c r="B96" s="5">
         <v>94</v>
       </c>
-      <c r="C96" s="1" t="b">
+      <c r="C96" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>604</v>
       </c>
       <c r="B97" s="5">
         <v>95</v>
       </c>
-      <c r="C97" s="1" t="b">
+      <c r="C97" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>605</v>
       </c>
       <c r="B98" s="5">
         <v>96</v>
       </c>
-      <c r="C98" s="1" t="b">
+      <c r="C98" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>606</v>
       </c>
       <c r="B99" s="5">
         <v>97</v>
       </c>
-      <c r="C99" s="1" t="b">
+      <c r="C99" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>607</v>
       </c>
       <c r="B100" s="5">
         <v>98</v>
       </c>
-      <c r="C100" s="1" t="b">
+      <c r="C100" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>608</v>
       </c>
       <c r="B101" s="5">
         <v>99</v>
       </c>
-      <c r="C101" s="1" t="b">
+      <c r="C101" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>275</v>
       </c>
       <c r="B102" s="5">
         <v>100</v>
       </c>
-      <c r="C102" s="1" t="b">
+      <c r="C102" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>276</v>
       </c>
       <c r="B103" s="5">
         <v>101</v>
       </c>
-      <c r="C103" s="1" t="b">
+      <c r="C103" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>277</v>
       </c>
       <c r="B104" s="5">
         <v>102</v>
       </c>
-      <c r="C104" s="1" t="b">
+      <c r="C104" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>278</v>
       </c>
       <c r="B105" s="5">
         <v>103</v>
       </c>
-      <c r="C105" s="1" t="b">
+      <c r="C105" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>279</v>
       </c>
       <c r="B106" s="5">
         <v>104</v>
       </c>
-      <c r="C106" s="1" t="b">
+      <c r="C106" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>280</v>
       </c>
       <c r="B107" s="5">
         <v>105</v>
       </c>
-      <c r="C107" s="1" t="b">
+      <c r="C107" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>281</v>
       </c>
       <c r="B108" s="5">
         <v>106</v>
       </c>
-      <c r="C108" s="1" t="b">
+      <c r="C108" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="M108" cm="1">
+        <f t="array" aca="1" ref="M108" ca="1">K108:M111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>282</v>
       </c>
       <c r="B109" s="5">
         <v>107</v>
       </c>
-      <c r="C109" s="1" t="b">
+      <c r="C109" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>283</v>
       </c>
       <c r="B110" s="5">
         <v>108</v>
       </c>
-      <c r="C110" s="1" t="b">
+      <c r="C110" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>284</v>
       </c>
       <c r="B111" s="5">
         <v>109</v>
       </c>
-      <c r="C111" s="1" t="b">
+      <c r="C111" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>285</v>
       </c>
       <c r="B112" s="5">
         <v>110</v>
       </c>
-      <c r="C112" s="1" t="b">
+      <c r="C112" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55925,7 +55936,7 @@
       <c r="B113" s="5">
         <v>111</v>
       </c>
-      <c r="C113" s="1" t="b">
+      <c r="C113" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55936,7 +55947,7 @@
       <c r="B114" s="5">
         <v>112</v>
       </c>
-      <c r="C114" s="1" t="b">
+      <c r="C114" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55947,7 +55958,7 @@
       <c r="B115" s="5">
         <v>113</v>
       </c>
-      <c r="C115" s="1" t="b">
+      <c r="C115" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55958,7 +55969,7 @@
       <c r="B116" s="5">
         <v>114</v>
       </c>
-      <c r="C116" s="1" t="b">
+      <c r="C116" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55969,7 +55980,7 @@
       <c r="B117" s="5">
         <v>115</v>
       </c>
-      <c r="C117" s="1" t="b">
+      <c r="C117" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55980,7 +55991,7 @@
       <c r="B118" s="5">
         <v>116</v>
       </c>
-      <c r="C118" s="1" t="b">
+      <c r="C118" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -55991,7 +56002,7 @@
       <c r="B119" s="5">
         <v>117</v>
       </c>
-      <c r="C119" s="1" t="b">
+      <c r="C119" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56002,7 +56013,7 @@
       <c r="B120" s="5">
         <v>118</v>
       </c>
-      <c r="C120" s="1" t="b">
+      <c r="C120" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56013,7 +56024,7 @@
       <c r="B121" s="5">
         <v>119</v>
       </c>
-      <c r="C121" s="1" t="b">
+      <c r="C121" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56024,7 +56035,7 @@
       <c r="B122" s="5">
         <v>120</v>
       </c>
-      <c r="C122" s="1" t="b">
+      <c r="C122" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56035,7 +56046,7 @@
       <c r="B123" s="5">
         <v>121</v>
       </c>
-      <c r="C123" s="1" t="b">
+      <c r="C123" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56046,7 +56057,7 @@
       <c r="B124" s="5">
         <v>122</v>
       </c>
-      <c r="C124" s="1" t="b">
+      <c r="C124" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56057,7 +56068,7 @@
       <c r="B125" s="5">
         <v>123</v>
       </c>
-      <c r="C125" s="1" t="b">
+      <c r="C125" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56068,7 +56079,7 @@
       <c r="B126" s="5">
         <v>124</v>
       </c>
-      <c r="C126" s="1" t="b">
+      <c r="C126" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56079,7 +56090,7 @@
       <c r="B127" s="5">
         <v>125</v>
       </c>
-      <c r="C127" s="1" t="b">
+      <c r="C127" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56090,7 +56101,7 @@
       <c r="B128" s="5">
         <v>126</v>
       </c>
-      <c r="C128" s="1" t="b">
+      <c r="C128" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56101,7 +56112,7 @@
       <c r="B129" s="5">
         <v>127</v>
       </c>
-      <c r="C129" s="1" t="b">
+      <c r="C129" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56112,7 +56123,7 @@
       <c r="B130" s="5">
         <v>128</v>
       </c>
-      <c r="C130" s="1" t="b">
+      <c r="C130" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56123,7 +56134,7 @@
       <c r="B131" s="5">
         <v>129</v>
       </c>
-      <c r="C131" s="1" t="b">
+      <c r="C131" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56134,7 +56145,7 @@
       <c r="B132" s="5">
         <v>130</v>
       </c>
-      <c r="C132" s="1" t="b">
+      <c r="C132" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56145,7 +56156,7 @@
       <c r="B133" s="5">
         <v>131</v>
       </c>
-      <c r="C133" s="1" t="b">
+      <c r="C133" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56156,7 +56167,7 @@
       <c r="B134" s="5">
         <v>132</v>
       </c>
-      <c r="C134" s="1" t="b">
+      <c r="C134" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56167,7 +56178,7 @@
       <c r="B135" s="5">
         <v>133</v>
       </c>
-      <c r="C135" s="1" t="b">
+      <c r="C135" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56178,7 +56189,7 @@
       <c r="B136" s="5">
         <v>134</v>
       </c>
-      <c r="C136" s="1" t="b">
+      <c r="C136" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56189,7 +56200,7 @@
       <c r="B137" s="5">
         <v>135</v>
       </c>
-      <c r="C137" s="1" t="b">
+      <c r="C137" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56200,7 +56211,7 @@
       <c r="B138" s="5">
         <v>136</v>
       </c>
-      <c r="C138" s="1" t="b">
+      <c r="C138" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56211,7 +56222,7 @@
       <c r="B139" s="5">
         <v>137</v>
       </c>
-      <c r="C139" s="1" t="b">
+      <c r="C139" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56222,7 +56233,7 @@
       <c r="B140" s="5">
         <v>138</v>
       </c>
-      <c r="C140" s="1" t="b">
+      <c r="C140" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56233,7 +56244,7 @@
       <c r="B141" s="5">
         <v>139</v>
       </c>
-      <c r="C141" s="1" t="b">
+      <c r="C141" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56244,7 +56255,7 @@
       <c r="B142" s="5">
         <v>140</v>
       </c>
-      <c r="C142" s="1" t="b">
+      <c r="C142" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56255,7 +56266,7 @@
       <c r="B143" s="5">
         <v>141</v>
       </c>
-      <c r="C143" s="1" t="b">
+      <c r="C143" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56266,7 +56277,7 @@
       <c r="B144" s="5">
         <v>142</v>
       </c>
-      <c r="C144" s="1" t="b">
+      <c r="C144" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56277,7 +56288,7 @@
       <c r="B145" s="5">
         <v>143</v>
       </c>
-      <c r="C145" s="1" t="b">
+      <c r="C145" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56288,7 +56299,7 @@
       <c r="B146" s="5">
         <v>144</v>
       </c>
-      <c r="C146" s="1" t="b">
+      <c r="C146" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56299,7 +56310,7 @@
       <c r="B147" s="5">
         <v>145</v>
       </c>
-      <c r="C147" s="1" t="b">
+      <c r="C147" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56310,7 +56321,7 @@
       <c r="B148" s="5">
         <v>146</v>
       </c>
-      <c r="C148" s="1" t="b">
+      <c r="C148" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56321,7 +56332,7 @@
       <c r="B149" s="5">
         <v>147</v>
       </c>
-      <c r="C149" s="1" t="b">
+      <c r="C149" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56332,7 +56343,7 @@
       <c r="B150" s="5">
         <v>148</v>
       </c>
-      <c r="C150" s="1" t="b">
+      <c r="C150" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56343,7 +56354,7 @@
       <c r="B151" s="5">
         <v>149</v>
       </c>
-      <c r="C151" s="1" t="b">
+      <c r="C151" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56354,7 +56365,7 @@
       <c r="B152" s="5">
         <v>150</v>
       </c>
-      <c r="C152" s="1" t="b">
+      <c r="C152" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56365,7 +56376,7 @@
       <c r="B153" s="5">
         <v>151</v>
       </c>
-      <c r="C153" s="1" t="b">
+      <c r="C153" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56376,7 +56387,7 @@
       <c r="B154" s="5">
         <v>152</v>
       </c>
-      <c r="C154" s="1" t="b">
+      <c r="C154" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56387,7 +56398,7 @@
       <c r="B155" s="5">
         <v>153</v>
       </c>
-      <c r="C155" s="1" t="b">
+      <c r="C155" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56398,7 +56409,7 @@
       <c r="B156" s="5">
         <v>154</v>
       </c>
-      <c r="C156" s="1" t="b">
+      <c r="C156" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56409,7 +56420,7 @@
       <c r="B157" s="5">
         <v>155</v>
       </c>
-      <c r="C157" s="1" t="b">
+      <c r="C157" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56420,7 +56431,7 @@
       <c r="B158" s="5">
         <v>156</v>
       </c>
-      <c r="C158" s="1" t="b">
+      <c r="C158" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56431,7 +56442,7 @@
       <c r="B159" s="5">
         <v>157</v>
       </c>
-      <c r="C159" s="1" t="b">
+      <c r="C159" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56442,7 +56453,7 @@
       <c r="B160" s="5">
         <v>158</v>
       </c>
-      <c r="C160" s="1" t="b">
+      <c r="C160" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56453,7 +56464,7 @@
       <c r="B161" s="5">
         <v>159</v>
       </c>
-      <c r="C161" s="1" t="b">
+      <c r="C161" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56464,7 +56475,7 @@
       <c r="B162" s="5">
         <v>160</v>
       </c>
-      <c r="C162" s="1" t="b">
+      <c r="C162" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56475,7 +56486,7 @@
       <c r="B163" s="5">
         <v>161</v>
       </c>
-      <c r="C163" s="1" t="b">
+      <c r="C163" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56486,7 +56497,7 @@
       <c r="B164" s="5">
         <v>162</v>
       </c>
-      <c r="C164" s="1" t="b">
+      <c r="C164" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56497,7 +56508,7 @@
       <c r="B165" s="5">
         <v>163</v>
       </c>
-      <c r="C165" s="1" t="b">
+      <c r="C165" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56508,7 +56519,7 @@
       <c r="B166" s="5">
         <v>164</v>
       </c>
-      <c r="C166" s="1" t="b">
+      <c r="C166" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56519,7 +56530,7 @@
       <c r="B167" s="5">
         <v>165</v>
       </c>
-      <c r="C167" s="1" t="b">
+      <c r="C167" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56530,7 +56541,7 @@
       <c r="B168" s="5">
         <v>166</v>
       </c>
-      <c r="C168" s="1" t="b">
+      <c r="C168" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56541,7 +56552,7 @@
       <c r="B169" s="5">
         <v>167</v>
       </c>
-      <c r="C169" s="1" t="b">
+      <c r="C169" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56552,7 +56563,7 @@
       <c r="B170" s="5">
         <v>168</v>
       </c>
-      <c r="C170" s="1" t="b">
+      <c r="C170" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56563,7 +56574,7 @@
       <c r="B171" s="5">
         <v>169</v>
       </c>
-      <c r="C171" s="1" t="b">
+      <c r="C171" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56574,7 +56585,7 @@
       <c r="B172" s="5">
         <v>170</v>
       </c>
-      <c r="C172" s="1" t="b">
+      <c r="C172" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56585,7 +56596,7 @@
       <c r="B173" s="5">
         <v>171</v>
       </c>
-      <c r="C173" s="1" t="b">
+      <c r="C173" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56596,7 +56607,7 @@
       <c r="B174" s="5">
         <v>172</v>
       </c>
-      <c r="C174" s="1" t="b">
+      <c r="C174" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56607,7 +56618,7 @@
       <c r="B175" s="5">
         <v>173</v>
       </c>
-      <c r="C175" s="1" t="b">
+      <c r="C175" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56618,7 +56629,7 @@
       <c r="B176" s="5">
         <v>174</v>
       </c>
-      <c r="C176" s="1" t="b">
+      <c r="C176" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56629,7 +56640,7 @@
       <c r="B177" s="5">
         <v>175</v>
       </c>
-      <c r="C177" s="1" t="b">
+      <c r="C177" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56640,7 +56651,7 @@
       <c r="B178" s="5">
         <v>176</v>
       </c>
-      <c r="C178" s="1" t="b">
+      <c r="C178" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56651,7 +56662,7 @@
       <c r="B179" s="5">
         <v>177</v>
       </c>
-      <c r="C179" s="1" t="b">
+      <c r="C179" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56662,7 +56673,7 @@
       <c r="B180" s="5">
         <v>178</v>
       </c>
-      <c r="C180" s="1" t="b">
+      <c r="C180" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56673,7 +56684,7 @@
       <c r="B181" s="5">
         <v>179</v>
       </c>
-      <c r="C181" s="1" t="b">
+      <c r="C181" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56684,7 +56695,7 @@
       <c r="B182" s="5">
         <v>180</v>
       </c>
-      <c r="C182" s="1" t="b">
+      <c r="C182" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56695,7 +56706,7 @@
       <c r="B183" s="5">
         <v>181</v>
       </c>
-      <c r="C183" s="1" t="b">
+      <c r="C183" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56706,7 +56717,7 @@
       <c r="B184" s="5">
         <v>182</v>
       </c>
-      <c r="C184" s="1" t="b">
+      <c r="C184" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56717,7 +56728,7 @@
       <c r="B185" s="5">
         <v>183</v>
       </c>
-      <c r="C185" s="1" t="b">
+      <c r="C185" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56728,7 +56739,7 @@
       <c r="B186" s="5">
         <v>184</v>
       </c>
-      <c r="C186" s="1" t="b">
+      <c r="C186" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56739,7 +56750,7 @@
       <c r="B187" s="5">
         <v>185</v>
       </c>
-      <c r="C187" s="1" t="b">
+      <c r="C187" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56750,7 +56761,7 @@
       <c r="B188" s="5">
         <v>186</v>
       </c>
-      <c r="C188" s="1" t="b">
+      <c r="C188" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56761,7 +56772,7 @@
       <c r="B189" s="5">
         <v>187</v>
       </c>
-      <c r="C189" s="1" t="b">
+      <c r="C189" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56772,7 +56783,7 @@
       <c r="B190" s="5">
         <v>188</v>
       </c>
-      <c r="C190" s="1" t="b">
+      <c r="C190" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56783,19 +56794,19 @@
       <c r="B191" s="5">
         <v>189</v>
       </c>
-      <c r="C191" s="1" t="b">
+      <c r="C191" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>365</v>
       </c>
       <c r="B192" s="5">
         <v>190</v>
       </c>
-      <c r="C192" s="1" t="b">
-        <v>1</v>
+      <c r="C192" s="6" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
@@ -56805,7 +56816,7 @@
       <c r="B193" s="5">
         <v>191</v>
       </c>
-      <c r="C193" s="1" t="b">
+      <c r="C193" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56816,7 +56827,7 @@
       <c r="B194" s="5">
         <v>192</v>
       </c>
-      <c r="C194" s="1" t="b">
+      <c r="C194" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56827,7 +56838,7 @@
       <c r="B195" s="5">
         <v>193</v>
       </c>
-      <c r="C195" s="1" t="b">
+      <c r="C195" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56838,7 +56849,7 @@
       <c r="B196" s="5">
         <v>194</v>
       </c>
-      <c r="C196" s="1" t="b">
+      <c r="C196" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56849,7 +56860,7 @@
       <c r="B197" s="5">
         <v>195</v>
       </c>
-      <c r="C197" s="1" t="b">
+      <c r="C197" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56860,30 +56871,30 @@
       <c r="B198" s="5">
         <v>196</v>
       </c>
-      <c r="C198" s="1" t="b">
+      <c r="C198" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>372</v>
       </c>
       <c r="B199" s="5">
         <v>197</v>
       </c>
-      <c r="C199" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C199" s="6" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>373</v>
       </c>
       <c r="B200" s="5">
         <v>198</v>
       </c>
-      <c r="C200" s="1" t="b">
-        <v>1</v>
+      <c r="C200" s="6" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -56893,7 +56904,7 @@
       <c r="B201" s="5">
         <v>199</v>
       </c>
-      <c r="C201" s="1" t="b">
+      <c r="C201" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56904,7 +56915,7 @@
       <c r="B202" s="5">
         <v>200</v>
       </c>
-      <c r="C202" s="1" t="b">
+      <c r="C202" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56915,7 +56926,7 @@
       <c r="B203" s="5">
         <v>201</v>
       </c>
-      <c r="C203" s="1" t="b">
+      <c r="C203" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56926,7 +56937,7 @@
       <c r="B204" s="5">
         <v>202</v>
       </c>
-      <c r="C204" s="1" t="b">
+      <c r="C204" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56937,7 +56948,7 @@
       <c r="B205" s="5">
         <v>203</v>
       </c>
-      <c r="C205" s="1" t="b">
+      <c r="C205" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56948,7 +56959,7 @@
       <c r="B206" s="5">
         <v>204</v>
       </c>
-      <c r="C206" s="1" t="b">
+      <c r="C206" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56959,7 +56970,7 @@
       <c r="B207" s="5">
         <v>205</v>
       </c>
-      <c r="C207" s="1" t="b">
+      <c r="C207" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56970,7 +56981,7 @@
       <c r="B208" s="5">
         <v>206</v>
       </c>
-      <c r="C208" s="1" t="b">
+      <c r="C208" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56981,7 +56992,7 @@
       <c r="B209" s="5">
         <v>207</v>
       </c>
-      <c r="C209" s="1" t="b">
+      <c r="C209" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -56992,7 +57003,7 @@
       <c r="B210" s="5">
         <v>208</v>
       </c>
-      <c r="C210" s="1" t="b">
+      <c r="C210" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57003,7 +57014,7 @@
       <c r="B211" s="5">
         <v>209</v>
       </c>
-      <c r="C211" s="1" t="b">
+      <c r="C211" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57014,7 +57025,7 @@
       <c r="B212" s="5">
         <v>210</v>
       </c>
-      <c r="C212" s="1" t="b">
+      <c r="C212" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57025,7 +57036,7 @@
       <c r="B213" s="5">
         <v>211</v>
       </c>
-      <c r="C213" s="1" t="b">
+      <c r="C213" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57036,19 +57047,19 @@
       <c r="B214" s="5">
         <v>212</v>
       </c>
-      <c r="C214" s="1" t="b">
+      <c r="C214" s="6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>388</v>
       </c>
       <c r="B215" s="5">
         <v>213</v>
       </c>
-      <c r="C215" s="1" t="b">
-        <v>1</v>
+      <c r="C215" s="6" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -57058,7 +57069,7 @@
       <c r="B216" s="5">
         <v>214</v>
       </c>
-      <c r="C216" s="1" t="b">
+      <c r="C216" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57069,7 +57080,7 @@
       <c r="B217" s="5">
         <v>215</v>
       </c>
-      <c r="C217" s="1" t="b">
+      <c r="C217" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57081,7 +57092,7 @@
         <v>216</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>507</v>
+        <v>610</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -57091,7 +57102,7 @@
       <c r="B219" s="5">
         <v>217</v>
       </c>
-      <c r="C219" s="1" t="b">
+      <c r="C219" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57102,7 +57113,7 @@
       <c r="B220" s="5">
         <v>218</v>
       </c>
-      <c r="C220" s="1" t="b">
+      <c r="C220" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57113,7 +57124,7 @@
       <c r="B221" s="5">
         <v>219</v>
       </c>
-      <c r="C221" s="1" t="b">
+      <c r="C221" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57124,7 +57135,7 @@
       <c r="B222" s="5">
         <v>220</v>
       </c>
-      <c r="C222" s="1" t="b">
+      <c r="C222" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57135,7 +57146,7 @@
       <c r="B223" s="5">
         <v>221</v>
       </c>
-      <c r="C223" s="1" t="b">
+      <c r="C223" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57146,7 +57157,7 @@
       <c r="B224" s="5">
         <v>222</v>
       </c>
-      <c r="C224" s="1" t="b">
+      <c r="C224" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57157,7 +57168,7 @@
       <c r="B225" s="5">
         <v>223</v>
       </c>
-      <c r="C225" s="1" t="b">
+      <c r="C225" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57168,7 +57179,7 @@
       <c r="B226" s="5">
         <v>224</v>
       </c>
-      <c r="C226" s="1" t="b">
+      <c r="C226" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57179,7 +57190,7 @@
       <c r="B227" s="5">
         <v>225</v>
       </c>
-      <c r="C227" s="1" t="b">
+      <c r="C227" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57190,7 +57201,7 @@
       <c r="B228" s="5">
         <v>226</v>
       </c>
-      <c r="C228" s="1" t="b">
+      <c r="C228" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57201,7 +57212,7 @@
       <c r="B229" s="5">
         <v>227</v>
       </c>
-      <c r="C229" s="1" t="b">
+      <c r="C229" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57212,7 +57223,7 @@
       <c r="B230" s="5">
         <v>228</v>
       </c>
-      <c r="C230" s="1" t="b">
+      <c r="C230" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57223,7 +57234,7 @@
       <c r="B231" s="5">
         <v>229</v>
       </c>
-      <c r="C231" s="1" t="b">
+      <c r="C231" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57234,7 +57245,7 @@
       <c r="B232" s="5">
         <v>230</v>
       </c>
-      <c r="C232" s="1" t="b">
+      <c r="C232" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57245,7 +57256,7 @@
       <c r="B233" s="5">
         <v>231</v>
       </c>
-      <c r="C233" s="1" t="b">
+      <c r="C233" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57256,7 +57267,7 @@
       <c r="B234" s="5">
         <v>232</v>
       </c>
-      <c r="C234" s="1" t="b">
+      <c r="C234" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57267,7 +57278,7 @@
       <c r="B235" s="5">
         <v>233</v>
       </c>
-      <c r="C235" s="1" t="b">
+      <c r="C235" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57278,7 +57289,7 @@
       <c r="B236" s="5">
         <v>234</v>
       </c>
-      <c r="C236" s="1" t="b">
+      <c r="C236" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57289,7 +57300,7 @@
       <c r="B237" s="5">
         <v>235</v>
       </c>
-      <c r="C237" s="1" t="b">
+      <c r="C237" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57300,7 +57311,7 @@
       <c r="B238" s="5">
         <v>236</v>
       </c>
-      <c r="C238" s="1" t="b">
+      <c r="C238" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57311,7 +57322,7 @@
       <c r="B239" s="5">
         <v>237</v>
       </c>
-      <c r="C239" s="1" t="b">
+      <c r="C239" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57322,7 +57333,7 @@
       <c r="B240" s="5">
         <v>238</v>
       </c>
-      <c r="C240" s="1" t="b">
+      <c r="C240" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57333,7 +57344,7 @@
       <c r="B241" s="5">
         <v>239</v>
       </c>
-      <c r="C241" s="1" t="b">
+      <c r="C241" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57344,7 +57355,7 @@
       <c r="B242" s="5">
         <v>240</v>
       </c>
-      <c r="C242" s="1" t="b">
+      <c r="C242" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57355,7 +57366,7 @@
       <c r="B243" s="5">
         <v>241</v>
       </c>
-      <c r="C243" s="1" t="b">
+      <c r="C243" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57366,7 +57377,7 @@
       <c r="B244" s="5">
         <v>242</v>
       </c>
-      <c r="C244" s="1" t="b">
+      <c r="C244" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57377,7 +57388,7 @@
       <c r="B245" s="5">
         <v>243</v>
       </c>
-      <c r="C245" s="1" t="b">
+      <c r="C245" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57388,7 +57399,7 @@
       <c r="B246" s="5">
         <v>244</v>
       </c>
-      <c r="C246" s="1" t="b">
+      <c r="C246" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57399,7 +57410,7 @@
       <c r="B247" s="5">
         <v>245</v>
       </c>
-      <c r="C247" s="1" t="b">
+      <c r="C247" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57410,7 +57421,7 @@
       <c r="B248" s="5">
         <v>246</v>
       </c>
-      <c r="C248" s="1" t="b">
+      <c r="C248" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57421,7 +57432,7 @@
       <c r="B249" s="5">
         <v>247</v>
       </c>
-      <c r="C249" s="1" t="b">
+      <c r="C249" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57432,7 +57443,7 @@
       <c r="B250" s="5">
         <v>248</v>
       </c>
-      <c r="C250" s="1" t="b">
+      <c r="C250" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57443,7 +57454,7 @@
       <c r="B251" s="5">
         <v>249</v>
       </c>
-      <c r="C251" s="1" t="b">
+      <c r="C251" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57454,7 +57465,7 @@
       <c r="B252" s="5">
         <v>250</v>
       </c>
-      <c r="C252" s="1" t="b">
+      <c r="C252" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57465,7 +57476,7 @@
       <c r="B253" s="5">
         <v>251</v>
       </c>
-      <c r="C253" s="1" t="b">
+      <c r="C253" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57476,7 +57487,7 @@
       <c r="B254" s="5">
         <v>252</v>
       </c>
-      <c r="C254" s="1" t="b">
+      <c r="C254" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57487,7 +57498,7 @@
       <c r="B255" s="5">
         <v>253</v>
       </c>
-      <c r="C255" s="1" t="b">
+      <c r="C255" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57498,7 +57509,7 @@
       <c r="B256" s="5">
         <v>254</v>
       </c>
-      <c r="C256" s="1" t="b">
+      <c r="C256" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57509,7 +57520,7 @@
       <c r="B257" s="5">
         <v>255</v>
       </c>
-      <c r="C257" s="1" t="b">
+      <c r="C257" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57520,7 +57531,7 @@
       <c r="B258" s="5">
         <v>256</v>
       </c>
-      <c r="C258" s="1" t="b">
+      <c r="C258" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57531,7 +57542,7 @@
       <c r="B259" s="5">
         <v>257</v>
       </c>
-      <c r="C259" s="1" t="b">
+      <c r="C259" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57542,7 +57553,7 @@
       <c r="B260" s="5">
         <v>258</v>
       </c>
-      <c r="C260" s="1" t="b">
+      <c r="C260" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57553,7 +57564,7 @@
       <c r="B261" s="5">
         <v>259</v>
       </c>
-      <c r="C261" s="1" t="b">
+      <c r="C261" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57564,7 +57575,7 @@
       <c r="B262" s="5">
         <v>260</v>
       </c>
-      <c r="C262" s="1" t="b">
+      <c r="C262" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57575,7 +57586,7 @@
       <c r="B263" s="5">
         <v>261</v>
       </c>
-      <c r="C263" s="1" t="b">
+      <c r="C263" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57586,7 +57597,7 @@
       <c r="B264" s="5">
         <v>262</v>
       </c>
-      <c r="C264" s="1" t="b">
+      <c r="C264" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57597,7 +57608,7 @@
       <c r="B265" s="5">
         <v>263</v>
       </c>
-      <c r="C265" s="1" t="b">
+      <c r="C265" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57608,7 +57619,7 @@
       <c r="B266" s="5">
         <v>264</v>
       </c>
-      <c r="C266" s="1" t="b">
+      <c r="C266" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57619,7 +57630,7 @@
       <c r="B267" s="5">
         <v>265</v>
       </c>
-      <c r="C267" s="1" t="b">
+      <c r="C267" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57630,7 +57641,7 @@
       <c r="B268" s="5">
         <v>266</v>
       </c>
-      <c r="C268" s="1" t="b">
+      <c r="C268" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57641,7 +57652,7 @@
       <c r="B269" s="5">
         <v>267</v>
       </c>
-      <c r="C269" s="1" t="b">
+      <c r="C269" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57652,7 +57663,7 @@
       <c r="B270" s="5">
         <v>268</v>
       </c>
-      <c r="C270" s="1" t="b">
+      <c r="C270" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57663,7 +57674,7 @@
       <c r="B271" s="5">
         <v>269</v>
       </c>
-      <c r="C271" s="1" t="b">
+      <c r="C271" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57674,7 +57685,7 @@
       <c r="B272" s="5">
         <v>270</v>
       </c>
-      <c r="C272" s="1" t="b">
+      <c r="C272" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57685,7 +57696,7 @@
       <c r="B273" s="5">
         <v>271</v>
       </c>
-      <c r="C273" s="1" t="b">
+      <c r="C273" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57696,7 +57707,7 @@
       <c r="B274" s="5">
         <v>272</v>
       </c>
-      <c r="C274" s="1" t="b">
+      <c r="C274" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57707,7 +57718,7 @@
       <c r="B275" s="5">
         <v>273</v>
       </c>
-      <c r="C275" s="1" t="b">
+      <c r="C275" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57718,7 +57729,7 @@
       <c r="B276" s="5">
         <v>274</v>
       </c>
-      <c r="C276" s="1" t="b">
+      <c r="C276" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57729,7 +57740,7 @@
       <c r="B277" s="5">
         <v>275</v>
       </c>
-      <c r="C277" s="1" t="b">
+      <c r="C277" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57740,7 +57751,7 @@
       <c r="B278" s="5">
         <v>276</v>
       </c>
-      <c r="C278" s="1" t="b">
+      <c r="C278" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57751,7 +57762,7 @@
       <c r="B279" s="5">
         <v>277</v>
       </c>
-      <c r="C279" s="1" t="b">
+      <c r="C279" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57762,7 +57773,7 @@
       <c r="B280" s="5">
         <v>278</v>
       </c>
-      <c r="C280" s="1" t="b">
+      <c r="C280" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57773,7 +57784,7 @@
       <c r="B281" s="5">
         <v>279</v>
       </c>
-      <c r="C281" s="1" t="b">
+      <c r="C281" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57784,7 +57795,7 @@
       <c r="B282" s="5">
         <v>280</v>
       </c>
-      <c r="C282" s="1" t="b">
+      <c r="C282" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57795,7 +57806,7 @@
       <c r="B283" s="5">
         <v>281</v>
       </c>
-      <c r="C283" s="1" t="b">
+      <c r="C283" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57806,7 +57817,7 @@
       <c r="B284" s="5">
         <v>282</v>
       </c>
-      <c r="C284" s="1" t="b">
+      <c r="C284" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57817,7 +57828,7 @@
       <c r="B285" s="5">
         <v>283</v>
       </c>
-      <c r="C285" s="1" t="b">
+      <c r="C285" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57828,7 +57839,7 @@
       <c r="B286" s="5">
         <v>284</v>
       </c>
-      <c r="C286" s="1" t="b">
+      <c r="C286" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57839,7 +57850,7 @@
       <c r="B287" s="5">
         <v>285</v>
       </c>
-      <c r="C287" s="1" t="b">
+      <c r="C287" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57861,7 +57872,7 @@
       <c r="B289" s="5">
         <v>287</v>
       </c>
-      <c r="C289" s="1" t="b">
+      <c r="C289" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57872,7 +57883,7 @@
       <c r="B290" s="5">
         <v>288</v>
       </c>
-      <c r="C290" s="1" t="b">
+      <c r="C290" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57883,7 +57894,7 @@
       <c r="B291" s="5">
         <v>289</v>
       </c>
-      <c r="C291" s="1" t="b">
+      <c r="C291" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57894,7 +57905,7 @@
       <c r="B292" s="5">
         <v>290</v>
       </c>
-      <c r="C292" s="1" t="b">
+      <c r="C292" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57905,7 +57916,7 @@
       <c r="B293" s="5">
         <v>291</v>
       </c>
-      <c r="C293" s="1" t="b">
+      <c r="C293" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57916,7 +57927,7 @@
       <c r="B294" s="5">
         <v>292</v>
       </c>
-      <c r="C294" s="1" t="b">
+      <c r="C294" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57927,7 +57938,7 @@
       <c r="B295" s="5">
         <v>293</v>
       </c>
-      <c r="C295" s="1" t="b">
+      <c r="C295" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57938,7 +57949,7 @@
       <c r="B296" s="5">
         <v>294</v>
       </c>
-      <c r="C296" s="1" t="b">
+      <c r="C296" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57949,7 +57960,7 @@
       <c r="B297" s="5">
         <v>295</v>
       </c>
-      <c r="C297" s="1" t="b">
+      <c r="C297" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57960,7 +57971,7 @@
       <c r="B298" s="5">
         <v>296</v>
       </c>
-      <c r="C298" s="1" t="b">
+      <c r="C298" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57971,7 +57982,7 @@
       <c r="B299" s="5">
         <v>297</v>
       </c>
-      <c r="C299" s="1" t="b">
+      <c r="C299" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -57982,7 +57993,7 @@
       <c r="B300" s="5">
         <v>298</v>
       </c>
-      <c r="C300" s="1" t="b">
+      <c r="C300" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58015,7 +58026,7 @@
       <c r="B303" s="5">
         <v>301</v>
       </c>
-      <c r="C303" s="1" t="b">
+      <c r="C303" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58026,7 +58037,7 @@
       <c r="B304" s="5">
         <v>302</v>
       </c>
-      <c r="C304" s="1" t="b">
+      <c r="C304" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58037,7 +58048,7 @@
       <c r="B305" s="5">
         <v>303</v>
       </c>
-      <c r="C305" s="1" t="b">
+      <c r="C305" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58048,7 +58059,7 @@
       <c r="B306" s="5">
         <v>304</v>
       </c>
-      <c r="C306" s="1" t="b">
+      <c r="C306" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58059,7 +58070,7 @@
       <c r="B307" s="5">
         <v>305</v>
       </c>
-      <c r="C307" s="1" t="b">
+      <c r="C307" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58070,7 +58081,7 @@
       <c r="B308" s="5">
         <v>306</v>
       </c>
-      <c r="C308" s="1" t="b">
+      <c r="C308" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58081,7 +58092,7 @@
       <c r="B309" s="5">
         <v>307</v>
       </c>
-      <c r="C309" s="1" t="b">
+      <c r="C309" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58092,7 +58103,7 @@
       <c r="B310" s="5">
         <v>308</v>
       </c>
-      <c r="C310" s="1" t="b">
+      <c r="C310" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58103,7 +58114,7 @@
       <c r="B311" s="5">
         <v>309</v>
       </c>
-      <c r="C311" s="1" t="b">
+      <c r="C311" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58114,7 +58125,7 @@
       <c r="B312" s="5">
         <v>310</v>
       </c>
-      <c r="C312" s="1" t="b">
+      <c r="C312" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58125,7 +58136,7 @@
       <c r="B313" s="5">
         <v>311</v>
       </c>
-      <c r="C313" s="1" t="b">
+      <c r="C313" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58136,7 +58147,7 @@
       <c r="B314" s="5">
         <v>312</v>
       </c>
-      <c r="C314" s="1" t="b">
+      <c r="C314" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58147,7 +58158,7 @@
       <c r="B315" s="5">
         <v>313</v>
       </c>
-      <c r="C315" s="1" t="b">
+      <c r="C315" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58158,7 +58169,7 @@
       <c r="B316" s="5">
         <v>314</v>
       </c>
-      <c r="C316" s="1" t="b">
+      <c r="C316" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58169,7 +58180,7 @@
       <c r="B317" s="5">
         <v>315</v>
       </c>
-      <c r="C317" s="1" t="b">
+      <c r="C317" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58180,7 +58191,7 @@
       <c r="B318" s="5">
         <v>316</v>
       </c>
-      <c r="C318" s="1" t="b">
+      <c r="C318" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58191,7 +58202,7 @@
       <c r="B319" s="5">
         <v>317</v>
       </c>
-      <c r="C319" s="1" t="b">
+      <c r="C319" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58202,7 +58213,7 @@
       <c r="B320" s="5">
         <v>318</v>
       </c>
-      <c r="C320" s="1" t="b">
+      <c r="C320" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58213,7 +58224,7 @@
       <c r="B321" s="5">
         <v>319</v>
       </c>
-      <c r="C321" s="1" t="b">
+      <c r="C321" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58224,7 +58235,7 @@
       <c r="B322" s="5">
         <v>320</v>
       </c>
-      <c r="C322" s="1" t="b">
+      <c r="C322" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58235,7 +58246,7 @@
       <c r="B323" s="5">
         <v>321</v>
       </c>
-      <c r="C323" s="1" t="b">
+      <c r="C323" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58246,7 +58257,7 @@
       <c r="B324" s="5">
         <v>322</v>
       </c>
-      <c r="C324" s="1" t="b">
+      <c r="C324" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58257,7 +58268,7 @@
       <c r="B325" s="5">
         <v>323</v>
       </c>
-      <c r="C325" s="1" t="b">
+      <c r="C325" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58268,7 +58279,7 @@
       <c r="B326" s="5">
         <v>324</v>
       </c>
-      <c r="C326" s="1" t="b">
+      <c r="C326" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58290,7 +58301,7 @@
       <c r="B328" s="5">
         <v>326</v>
       </c>
-      <c r="C328" s="1" t="b">
+      <c r="C328" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58301,7 +58312,7 @@
       <c r="B329" s="5">
         <v>327</v>
       </c>
-      <c r="C329" s="1" t="b">
+      <c r="C329" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58312,7 +58323,7 @@
       <c r="B330" s="5">
         <v>328</v>
       </c>
-      <c r="C330" s="1" t="b">
+      <c r="C330" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58323,7 +58334,7 @@
       <c r="B331" s="5">
         <v>329</v>
       </c>
-      <c r="C331" s="1" t="b">
+      <c r="C331" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58334,7 +58345,7 @@
       <c r="B332" s="4">
         <v>330</v>
       </c>
-      <c r="C332" s="1" t="b">
+      <c r="C332" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58345,7 +58356,7 @@
       <c r="B333" s="4">
         <v>331</v>
       </c>
-      <c r="C333" s="1" t="b">
+      <c r="C333" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -58356,12 +58367,13 @@
       <c r="B334" s="4">
         <v>332</v>
       </c>
-      <c r="C334" s="1" t="b">
+      <c r="C334" s="6" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:C334" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
+  <autoFilter ref="A1:C335" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
     <filterColumn colId="2">
       <filters>
         <filter val="FALSE"/>

--- a/Snobol Functions.xlsx
+++ b/Snobol Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcooper\source\repos\Spitbol4Win\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B816028-3588-41C1-BEFD-51FC8E6DB92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB86804D-928B-4BEE-BDB1-A335233A1253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30324" yWindow="4956" windowWidth="13416" windowHeight="18816" activeTab="2" xr2:uid="{14808CA3-9D70-46D1-8654-4F03110B5BF1}"/>
+    <workbookView xWindow="25236" yWindow="3384" windowWidth="13416" windowHeight="18816" xr2:uid="{14808CA3-9D70-46D1-8654-4F03110B5BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Keywords" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Errors" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Errors!$A$1:$C$335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Errors!$A$1:$C$334</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Keywords!$A$1:$D$16631</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Testing!$A$1:$C$135</definedName>
   </definedNames>
@@ -40,28 +40,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -54684,8 +54662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:M335"/>
+  <dimension ref="A1:C334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" bestFit="1" customWidth="1"/>
@@ -54781,7 +54758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>516</v>
       </c>
@@ -54913,7 +54890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>528</v>
       </c>
@@ -55749,7 +55726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>604</v>
       </c>
@@ -55760,7 +55737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>605</v>
       </c>
@@ -55771,7 +55748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>606</v>
       </c>
@@ -55782,7 +55759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>607</v>
       </c>
@@ -55793,7 +55770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>608</v>
       </c>
@@ -55804,7 +55781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>275</v>
       </c>
@@ -55815,7 +55792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>276</v>
       </c>
@@ -55826,7 +55803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>277</v>
       </c>
@@ -55837,7 +55814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>278</v>
       </c>
@@ -55848,7 +55825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>279</v>
       </c>
@@ -55859,7 +55836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>280</v>
       </c>
@@ -55870,7 +55847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>281</v>
       </c>
@@ -55880,12 +55857,8 @@
       <c r="C108" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="M108" cm="1">
-        <f t="array" aca="1" ref="M108" ca="1">K108:M111</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>282</v>
       </c>
@@ -55896,7 +55869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>283</v>
       </c>
@@ -55907,7 +55880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>284</v>
       </c>
@@ -55918,7 +55891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>285</v>
       </c>
@@ -56798,7 +56771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>365</v>
       </c>
@@ -56875,7 +56848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>372</v>
       </c>
@@ -56886,7 +56859,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>373</v>
       </c>
@@ -57051,7 +57024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>388</v>
       </c>
@@ -57084,7 +57057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>391</v>
       </c>
@@ -57854,7 +57827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>461</v>
       </c>
@@ -57997,7 +57970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>474</v>
       </c>
@@ -58008,7 +57981,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>475</v>
       </c>
@@ -58283,7 +58256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>499</v>
       </c>
@@ -58371,16 +58344,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:C335" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="FALSE"/>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C334" xr:uid="{622B2D9F-4107-4DCD-B2B1-B371E0938450}"/>
   <conditionalFormatting sqref="C2:C334">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>TRUE</formula>
